--- a/data/season_26_27.xlsx
+++ b/data/season_26_27.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lukec\OneDrive\Documents\Rprojects\misc_projects\fpl_r\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9F7A65-F0D3-4A74-BABB-4E4B89488095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE83DAF2-574A-4275-ADB7-710CB65DBB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="842" xr2:uid="{782628A8-4822-4E84-B9D1-9E9F8CA74FCB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="842" activeTab="9" xr2:uid="{782628A8-4822-4E84-B9D1-9E9F8CA74FCB}"/>
   </bookViews>
   <sheets>
     <sheet name="season" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="193">
   <si>
     <t>gameweek_id</t>
   </si>
@@ -509,6 +509,111 @@
   </si>
   <si>
     <t>ARS (H)</t>
+  </si>
+  <si>
+    <t>TC1</t>
+  </si>
+  <si>
+    <t>WC1</t>
+  </si>
+  <si>
+    <t>Mbeumo</t>
+  </si>
+  <si>
+    <t>Cherki</t>
+  </si>
+  <si>
+    <t>Lammens</t>
+  </si>
+  <si>
+    <t>Leno</t>
+  </si>
+  <si>
+    <t>jameslm</t>
+  </si>
+  <si>
+    <t>Hincapie</t>
+  </si>
+  <si>
+    <t>Konsa</t>
+  </si>
+  <si>
+    <t>lewis</t>
+  </si>
+  <si>
+    <t>Szoboszlai</t>
+  </si>
+  <si>
+    <t>Isak</t>
+  </si>
+  <si>
+    <t>João Pedro</t>
+  </si>
+  <si>
+    <t>CHE (H)</t>
+  </si>
+  <si>
+    <t>Done (66)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cherki </t>
+  </si>
+  <si>
+    <t>Done (65)</t>
+  </si>
+  <si>
+    <t>LIV (H)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mosquera keyboard_arrow_down lens error </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konsa keyboard_arrow_up </t>
+  </si>
+  <si>
+    <t>MCI (A)</t>
+  </si>
+  <si>
+    <t>Done (86)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leno </t>
+  </si>
+  <si>
+    <t>Done (26)</t>
+  </si>
+  <si>
+    <t>MUN (H)</t>
+  </si>
+  <si>
+    <t>Done (74)</t>
+  </si>
+  <si>
+    <t>Done (83)</t>
+  </si>
+  <si>
+    <t>Done (31)</t>
+  </si>
+  <si>
+    <t>Done (16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tzolakis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gvardiol </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajayi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wissa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayode </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarkowski </t>
   </si>
 </sst>
 </file>
@@ -554,7 +659,53 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -734,16 +885,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}" name="Table1" displayName="Table1" ref="A1:J17" totalsRowShown="0">
-  <autoFilter ref="A1:J17" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}" name="Table1" displayName="Table1" ref="A1:J25" totalsRowShown="0">
+  <autoFilter ref="A1:J25" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{3DFDA157-BD05-4F91-BBC2-46C272CA2753}" name="date"/>
     <tableColumn id="2" xr3:uid="{E77E158C-7AE3-4435-9E81-D58EA8264AE1}" name="gameweek_id"/>
     <tableColumn id="3" xr3:uid="{4EC2B4AA-BB48-4F1C-AA23-865B4955D775}" name="season_standing"/>
     <tableColumn id="4" xr3:uid="{1A5CC8A7-E0BF-4423-9565-863589D0157E}" name="team"/>
-    <tableColumn id="5" xr3:uid="{7F46AE02-3FA0-4946-9C0E-9C4075370946}" name="season_transfers" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{CD26F816-00C7-4F1F-B5FB-E9B2D89B04C7}" name="overall_rank" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{4035F136-3D22-4E3D-951A-6F27496E67CD}" name="team_value" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{7F46AE02-3FA0-4946-9C0E-9C4075370946}" name="season_transfers" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{CD26F816-00C7-4F1F-B5FB-E9B2D89B04C7}" name="overall_rank" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{4035F136-3D22-4E3D-951A-6F27496E67CD}" name="team_value" dataDxfId="14"/>
     <tableColumn id="8" xr3:uid="{873B883E-CCA1-4415-9B58-AC7C5BD906B9}" name="gw_net"/>
     <tableColumn id="9" xr3:uid="{C348C7FD-EAB4-47B7-9C3E-0CF639A77318}" name="total"/>
     <tableColumn id="10" xr3:uid="{29219B07-DFC0-4696-B9A2-8E2F83EBFA88}" name="chip"/>
@@ -753,8 +904,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}" name="tim" displayName="tim" ref="A1:H31" totalsRowShown="0">
-  <autoFilter ref="A1:H31" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}" name="tim" displayName="tim" ref="A1:H46" totalsRowShown="0">
+  <autoFilter ref="A1:H46" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{67AFB369-C03A-462B-972F-AF60CDE2CFAB}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{44789776-FE7D-494A-B94B-2A601E85CB98}" name="player_slot"/>
@@ -770,8 +921,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}" name="Table6" displayName="Table6" ref="A1:G4" totalsRowShown="0">
-  <autoFilter ref="A1:G4" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}" name="Table6" displayName="Table6" ref="A1:G9" totalsRowShown="0">
+  <autoFilter ref="A1:G9" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G2">
     <sortCondition ref="A1:A2"/>
   </sortState>
@@ -789,16 +940,16 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}" name="luke" displayName="luke" ref="A1:H31" totalsRowShown="0">
-  <autoFilter ref="A1:H31" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}" name="luke" displayName="luke" ref="A1:H46" totalsRowShown="0">
+  <autoFilter ref="A1:H46" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{E03C2832-F763-487D-BAF0-A846252C195D}" name="gameweek_id"/>
     <tableColumn id="7" xr3:uid="{442DEA06-1307-4EEB-981E-C530D39C1221}" name="player_slot"/>
     <tableColumn id="2" xr3:uid="{BE1D58D1-9C51-42D3-AA22-8CAB28CF8604}" name="player"/>
     <tableColumn id="3" xr3:uid="{BBA3FCC6-806B-41EB-9798-388AD565061B}" name="opposition"/>
     <tableColumn id="4" xr3:uid="{8A9B9F67-F40D-4762-ABF7-51D6948CCFB8}" name="status"/>
-    <tableColumn id="5" xr3:uid="{0F035BB3-B640-41E5-A9E0-B058E669931F}" name="points" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{0A20F07A-D2D6-40B3-BC30-00A5CB8DAF62}" name="importance" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{0F035BB3-B640-41E5-A9E0-B058E669931F}" name="points" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{0A20F07A-D2D6-40B3-BC30-00A5CB8DAF62}" name="importance" dataDxfId="12"/>
     <tableColumn id="8" xr3:uid="{D89A4728-D353-4540-BF9C-5C72EE4426C5}" name="captain"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -806,16 +957,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}" name="james_c" displayName="james_c" ref="A1:H31" totalsRowShown="0">
-  <autoFilter ref="A1:H31" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}" name="james_c" displayName="james_c" ref="A1:H46" totalsRowShown="0">
+  <autoFilter ref="A1:H46" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{E3512878-F631-4A83-9CF0-34024519F60B}" name="gameweek_id"/>
     <tableColumn id="7" xr3:uid="{FB753C77-F849-4945-8ED7-323A572ADEC0}" name="player_slot"/>
     <tableColumn id="2" xr3:uid="{A4B086A9-1D65-498E-82B0-9E3DDE205578}" name="player"/>
     <tableColumn id="3" xr3:uid="{EAFCFA61-49CF-4629-92EB-1845A9C161E8}" name="opposition"/>
     <tableColumn id="4" xr3:uid="{49DB9FCA-5CA9-48A1-8F9F-B6D2EEAFF45A}" name="status"/>
-    <tableColumn id="5" xr3:uid="{7BB11C7C-223D-4CF7-877E-24F3DB42AEEB}" name="points" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{E23E9A84-2244-4003-A5C3-AE72E5161746}" name="importance" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{7BB11C7C-223D-4CF7-877E-24F3DB42AEEB}" name="points" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{E23E9A84-2244-4003-A5C3-AE72E5161746}" name="importance" dataDxfId="10"/>
     <tableColumn id="8" xr3:uid="{3D20344A-A9A9-43E1-96DD-6D5E7E4D95B7}" name="captain"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -823,16 +974,16 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}" name="james_lm" displayName="james_lm" ref="A1:H31" totalsRowShown="0">
-  <autoFilter ref="A1:H31" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}" name="james_lm" displayName="james_lm" ref="A1:H46" totalsRowShown="0">
+  <autoFilter ref="A1:H46" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{85A61EA9-7D32-46E4-A518-261A47E355F4}" name="gameweek_id"/>
     <tableColumn id="7" xr3:uid="{86687FAE-12A2-4491-A6A8-B516A188A202}" name="player_slot"/>
     <tableColumn id="2" xr3:uid="{DDB067C6-F23D-40DD-9532-341379943214}" name="player"/>
     <tableColumn id="3" xr3:uid="{F61B9D23-0C8B-4F9C-9E09-DA9CF7A62D86}" name="opposition"/>
     <tableColumn id="4" xr3:uid="{F91D60CD-48C9-41AB-B219-B337A638004E}" name="status"/>
-    <tableColumn id="5" xr3:uid="{C9BD2123-E472-4AD8-B85E-08C7852BCADA}" name="points" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{D05930F1-9DF5-467C-8F3B-E6AAD4D53262}" name="importance" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{C9BD2123-E472-4AD8-B85E-08C7852BCADA}" name="points" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{D05930F1-9DF5-467C-8F3B-E6AAD4D53262}" name="importance" dataDxfId="8"/>
     <tableColumn id="8" xr3:uid="{2FE3DCC3-DA4C-4705-A219-64FBCE85BF11}" name="captain"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -840,8 +991,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}" name="fred" displayName="fred" ref="A1:H31" totalsRowShown="0">
-  <autoFilter ref="A1:H31" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}" name="fred" displayName="fred" ref="A1:H46" totalsRowShown="0">
+  <autoFilter ref="A1:H46" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{BD2A7E80-7899-44F4-A0E0-E1951D803BBF}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{9A789C6B-DF65-4741-842B-32F8E097183F}" name="player_slot"/>
@@ -857,8 +1008,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}" name="amy" displayName="amy" ref="A1:H31" totalsRowShown="0">
-  <autoFilter ref="A1:H31" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}" name="amy" displayName="amy" ref="A1:H46" totalsRowShown="0">
+  <autoFilter ref="A1:H46" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{3EEC9588-A154-4394-B1C6-FB872F361A10}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{CFDBEB1B-AC4B-4140-B9D5-FB0F16BBFA70}" name="player_slot"/>
@@ -874,8 +1025,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}" name="andy" displayName="andy" ref="A1:H31" totalsRowShown="0">
-  <autoFilter ref="A1:H31" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}" name="andy" displayName="andy" ref="A1:H46" totalsRowShown="0">
+  <autoFilter ref="A1:H46" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{25B33829-3E10-4EA1-9ED1-D911F47A3168}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{4C06A930-A949-45AD-BF12-6F05B56443BE}" name="player_slot"/>
@@ -891,8 +1042,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}" name="lewis" displayName="lewis" ref="A1:H31" totalsRowShown="0">
-  <autoFilter ref="A1:H31" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}" name="lewis" displayName="lewis" ref="A1:H46" totalsRowShown="0">
+  <autoFilter ref="A1:H46" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{14461CE9-1F87-4E76-B041-83CB47DED671}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{0AAB3767-3503-40AA-A974-A7C448E60023}" name="player_slot"/>
@@ -1693,7 +1844,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>46262</v>
       </c>
@@ -1722,14 +1873,275 @@
         <v>120</v>
       </c>
     </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>46269</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
+      </c>
+      <c r="F18" s="2">
+        <v>567858</v>
+      </c>
+      <c r="G18" s="2">
+        <v>100.6</v>
+      </c>
+      <c r="H18">
+        <v>50</v>
+      </c>
+      <c r="I18">
+        <v>222</v>
+      </c>
+      <c r="J18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>46269</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1784329</v>
+      </c>
+      <c r="G19">
+        <v>100.1</v>
+      </c>
+      <c r="H19">
+        <v>59</v>
+      </c>
+      <c r="I19">
+        <v>205</v>
+      </c>
+      <c r="J19" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>46269</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1982279</v>
+      </c>
+      <c r="G20">
+        <v>99.9</v>
+      </c>
+      <c r="H20">
+        <v>56</v>
+      </c>
+      <c r="I20">
+        <v>203</v>
+      </c>
+      <c r="J20" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>46269</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>2208110</v>
+      </c>
+      <c r="G21">
+        <v>99.8</v>
+      </c>
+      <c r="H21">
+        <v>64</v>
+      </c>
+      <c r="I21">
+        <v>201</v>
+      </c>
+      <c r="J21" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>46269</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+      <c r="C22">
+        <v>5</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="2">
+        <v>3</v>
+      </c>
+      <c r="F22" s="2">
+        <v>2871860</v>
+      </c>
+      <c r="G22">
+        <v>100.2</v>
+      </c>
+      <c r="H22">
+        <v>52</v>
+      </c>
+      <c r="I22">
+        <v>196</v>
+      </c>
+      <c r="J22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>46269</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>6</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2">
+        <v>3523110</v>
+      </c>
+      <c r="G23">
+        <v>100</v>
+      </c>
+      <c r="H23">
+        <v>62</v>
+      </c>
+      <c r="I23">
+        <v>190</v>
+      </c>
+      <c r="J23" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>46269</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24">
+        <v>7</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2">
+        <v>5818110</v>
+      </c>
+      <c r="G24">
+        <v>100.2</v>
+      </c>
+      <c r="H24">
+        <v>51</v>
+      </c>
+      <c r="I24">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>46269</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>6084360</v>
+      </c>
+      <c r="G25">
+        <v>100.7</v>
+      </c>
+      <c r="H25">
+        <v>50</v>
+      </c>
+      <c r="I25">
+        <v>170</v>
+      </c>
+      <c r="J25" t="s">
+        <v>159</v>
+      </c>
+    </row>
     <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <conditionalFormatting sqref="A2:J17">
-    <cfRule type="expression" dxfId="1" priority="3">
+  <conditionalFormatting sqref="A2:J25">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>MOD($B2, 2) = 1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>MOD($B2, 2) = 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18:C25">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>MOD($B18, 2) = 1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>MOD($B18, 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1741,7 +2153,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A820DAB-6033-4E1A-86E6-3C9D8203F219}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2469,6 +2881,357 @@
         <v>6</v>
       </c>
       <c r="G31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32">
+        <v>6</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+      <c r="H32" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>188</v>
+      </c>
+      <c r="D33" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" t="s">
+        <v>128</v>
+      </c>
+      <c r="F33">
+        <v>8</v>
+      </c>
+      <c r="G33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>3</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>189</v>
+      </c>
+      <c r="D34" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" t="s">
+        <v>128</v>
+      </c>
+      <c r="F34">
+        <v>5</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" t="s">
+        <v>171</v>
+      </c>
+      <c r="E35" t="s">
+        <v>172</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>3</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" t="s">
+        <v>171</v>
+      </c>
+      <c r="E36" t="s">
+        <v>128</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>3</v>
+      </c>
+      <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>173</v>
+      </c>
+      <c r="D37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" t="s">
+        <v>174</v>
+      </c>
+      <c r="F37">
+        <v>6</v>
+      </c>
+      <c r="G37" s="1">
+        <v>1.71</v>
+      </c>
+      <c r="H37" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>3</v>
+      </c>
+      <c r="B38">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>84</v>
+      </c>
+      <c r="D38" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" t="s">
+        <v>128</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>3</v>
+      </c>
+      <c r="B39">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" t="s">
+        <v>128</v>
+      </c>
+      <c r="F39">
+        <v>2</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>3</v>
+      </c>
+      <c r="B40">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" t="s">
+        <v>128</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>3</v>
+      </c>
+      <c r="B41">
+        <v>10</v>
+      </c>
+      <c r="C41" t="s">
+        <v>190</v>
+      </c>
+      <c r="D41" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" t="s">
+        <v>128</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>3</v>
+      </c>
+      <c r="B42">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>101</v>
+      </c>
+      <c r="D42" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" t="s">
+        <v>145</v>
+      </c>
+      <c r="F42">
+        <v>13</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>3</v>
+      </c>
+      <c r="B43">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" t="s">
+        <v>171</v>
+      </c>
+      <c r="E43" t="s">
+        <v>128</v>
+      </c>
+      <c r="F43">
+        <v>3</v>
+      </c>
+      <c r="G43" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
+        <v>191</v>
+      </c>
+      <c r="D44" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" t="s">
+        <v>133</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>3</v>
+      </c>
+      <c r="B45">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45" t="s">
+        <v>78</v>
+      </c>
+      <c r="E45" t="s">
+        <v>128</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>3</v>
+      </c>
+      <c r="B46">
+        <v>15</v>
+      </c>
+      <c r="C46" t="s">
+        <v>192</v>
+      </c>
+      <c r="D46" t="s">
+        <v>182</v>
+      </c>
+      <c r="E46" t="s">
+        <v>128</v>
+      </c>
+      <c r="F46">
+        <v>3</v>
+      </c>
+      <c r="G46" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2491,7 +3254,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330229B3-0B25-4B18-9D20-120CB711B0FB}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -2583,6 +3346,106 @@
         <v>4</v>
       </c>
     </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>161</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>163</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="F8" t="s">
+        <v>161</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D9">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -2593,7 +3456,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BFE37CD-4558-41F4-92EA-FE7453319710}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -3331,6 +4194,357 @@
         <v>0</v>
       </c>
     </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32" s="3">
+        <v>3</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" t="s">
+        <v>171</v>
+      </c>
+      <c r="E33" t="s">
+        <v>172</v>
+      </c>
+      <c r="F33" s="3">
+        <v>2</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>3</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" t="s">
+        <v>128</v>
+      </c>
+      <c r="F34" s="3">
+        <v>2</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" t="s">
+        <v>60</v>
+      </c>
+      <c r="E35" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="3">
+        <v>7</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>3</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" t="s">
+        <v>128</v>
+      </c>
+      <c r="F36" s="3">
+        <v>2</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>3</v>
+      </c>
+      <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>173</v>
+      </c>
+      <c r="D37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" t="s">
+        <v>174</v>
+      </c>
+      <c r="F37" s="3">
+        <v>3</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>3</v>
+      </c>
+      <c r="B38">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" t="s">
+        <v>63</v>
+      </c>
+      <c r="E38" t="s">
+        <v>133</v>
+      </c>
+      <c r="F38" s="3">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>3</v>
+      </c>
+      <c r="B39">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" t="s">
+        <v>128</v>
+      </c>
+      <c r="F39" s="3">
+        <v>2</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>3</v>
+      </c>
+      <c r="B40">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" t="s">
+        <v>128</v>
+      </c>
+      <c r="F40" s="3">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>3</v>
+      </c>
+      <c r="B41">
+        <v>10</v>
+      </c>
+      <c r="C41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" t="s">
+        <v>36</v>
+      </c>
+      <c r="E41" t="s">
+        <v>128</v>
+      </c>
+      <c r="F41" s="3">
+        <v>27</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H41" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>3</v>
+      </c>
+      <c r="B42">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" t="s">
+        <v>112</v>
+      </c>
+      <c r="E42" t="s">
+        <v>141</v>
+      </c>
+      <c r="F42" s="3">
+        <v>1</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>3</v>
+      </c>
+      <c r="B43">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" t="s">
+        <v>128</v>
+      </c>
+      <c r="F43" s="3">
+        <v>6</v>
+      </c>
+      <c r="G43" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44" t="s">
+        <v>47</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>3</v>
+      </c>
+      <c r="B45">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45" t="s">
+        <v>171</v>
+      </c>
+      <c r="E45" t="s">
+        <v>128</v>
+      </c>
+      <c r="F45" s="3">
+        <v>5</v>
+      </c>
+      <c r="G45" s="1">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>3</v>
+      </c>
+      <c r="B46">
+        <v>15</v>
+      </c>
+      <c r="C46" t="s">
+        <v>62</v>
+      </c>
+      <c r="D46" t="s">
+        <v>175</v>
+      </c>
+      <c r="E46" t="s">
+        <v>128</v>
+      </c>
+      <c r="F46" s="3">
+        <v>3</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3342,7 +4556,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A36F238-E413-4105-953D-9BEAF6AEF0DC}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
@@ -4076,6 +5290,357 @@
       </c>
       <c r="G31" s="1">
         <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32" s="3">
+        <v>3</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" t="s">
+        <v>128</v>
+      </c>
+      <c r="F33" s="3">
+        <v>4</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>3</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>176</v>
+      </c>
+      <c r="D34" t="s">
+        <v>171</v>
+      </c>
+      <c r="E34" t="s">
+        <v>47</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="3">
+        <v>8</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>3</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" t="s">
+        <v>171</v>
+      </c>
+      <c r="E36" t="s">
+        <v>128</v>
+      </c>
+      <c r="F36" s="3">
+        <v>5</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>3</v>
+      </c>
+      <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" t="s">
+        <v>128</v>
+      </c>
+      <c r="F37" s="3">
+        <v>2</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H37" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>3</v>
+      </c>
+      <c r="B38">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" t="s">
+        <v>128</v>
+      </c>
+      <c r="F38" s="3">
+        <v>3</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>3</v>
+      </c>
+      <c r="B39">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39" t="s">
+        <v>128</v>
+      </c>
+      <c r="F39" s="3">
+        <v>3</v>
+      </c>
+      <c r="G39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>3</v>
+      </c>
+      <c r="B40">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" t="s">
+        <v>128</v>
+      </c>
+      <c r="F40" s="3">
+        <v>2</v>
+      </c>
+      <c r="G40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>3</v>
+      </c>
+      <c r="B41">
+        <v>10</v>
+      </c>
+      <c r="C41" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E41" t="s">
+        <v>128</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>3</v>
+      </c>
+      <c r="B42">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" t="s">
+        <v>128</v>
+      </c>
+      <c r="F42" s="3">
+        <v>27</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H42" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>3</v>
+      </c>
+      <c r="B43">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" t="s">
+        <v>128</v>
+      </c>
+      <c r="F43" s="3">
+        <v>2</v>
+      </c>
+      <c r="G43" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" t="s">
+        <v>133</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>3</v>
+      </c>
+      <c r="B45">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>177</v>
+      </c>
+      <c r="D45" t="s">
+        <v>171</v>
+      </c>
+      <c r="E45" t="s">
+        <v>128</v>
+      </c>
+      <c r="F45" s="3">
+        <v>4</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>3</v>
+      </c>
+      <c r="B46">
+        <v>15</v>
+      </c>
+      <c r="C46" t="s">
+        <v>77</v>
+      </c>
+      <c r="D46" t="s">
+        <v>178</v>
+      </c>
+      <c r="E46" t="s">
+        <v>128</v>
+      </c>
+      <c r="F46" s="3">
+        <v>3</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4088,7 +5653,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0779779-8AAD-4A05-B64B-AAE55E86E147}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
@@ -4821,6 +6386,357 @@
         <v>6</v>
       </c>
       <c r="G31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32" s="3">
+        <v>3</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" t="s">
+        <v>171</v>
+      </c>
+      <c r="E33" t="s">
+        <v>172</v>
+      </c>
+      <c r="F33" s="3">
+        <v>2</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>3</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" t="s">
+        <v>128</v>
+      </c>
+      <c r="F34" s="3">
+        <v>4</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" t="s">
+        <v>60</v>
+      </c>
+      <c r="E35" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="3">
+        <v>7</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>3</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" t="s">
+        <v>128</v>
+      </c>
+      <c r="F36" s="3">
+        <v>2</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>3</v>
+      </c>
+      <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" t="s">
+        <v>128</v>
+      </c>
+      <c r="F37" s="3">
+        <v>6</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>3</v>
+      </c>
+      <c r="B38">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" t="s">
+        <v>128</v>
+      </c>
+      <c r="F38" s="3">
+        <v>3</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>3</v>
+      </c>
+      <c r="B39">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E39" t="s">
+        <v>179</v>
+      </c>
+      <c r="F39" s="3">
+        <v>3</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>3</v>
+      </c>
+      <c r="B40">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" t="s">
+        <v>128</v>
+      </c>
+      <c r="F40" s="3">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>3</v>
+      </c>
+      <c r="B41">
+        <v>10</v>
+      </c>
+      <c r="C41" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" t="s">
+        <v>112</v>
+      </c>
+      <c r="E41" t="s">
+        <v>141</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>3</v>
+      </c>
+      <c r="B42">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" t="s">
+        <v>128</v>
+      </c>
+      <c r="F42" s="3">
+        <v>27</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H42" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>3</v>
+      </c>
+      <c r="B43">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>180</v>
+      </c>
+      <c r="D43" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" t="s">
+        <v>128</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
+        <v>85</v>
+      </c>
+      <c r="D44" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" t="s">
+        <v>181</v>
+      </c>
+      <c r="F44" s="3">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>3</v>
+      </c>
+      <c r="B45">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>74</v>
+      </c>
+      <c r="D45" t="s">
+        <v>56</v>
+      </c>
+      <c r="E45" t="s">
+        <v>128</v>
+      </c>
+      <c r="F45" s="3">
+        <v>2</v>
+      </c>
+      <c r="G45" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>3</v>
+      </c>
+      <c r="B46">
+        <v>15</v>
+      </c>
+      <c r="C46" t="s">
+        <v>87</v>
+      </c>
+      <c r="D46" t="s">
+        <v>178</v>
+      </c>
+      <c r="E46" t="s">
+        <v>128</v>
+      </c>
+      <c r="F46" s="3">
+        <v>4</v>
+      </c>
+      <c r="G46" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4834,7 +6750,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{079AB974-BCF6-45DE-BAD2-52D6AC42558C}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -5572,6 +7488,357 @@
         <v>0</v>
       </c>
     </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" t="s">
+        <v>171</v>
+      </c>
+      <c r="E32" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32">
+        <v>3</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" t="s">
+        <v>171</v>
+      </c>
+      <c r="E33" t="s">
+        <v>128</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="H33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>3</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" t="s">
+        <v>128</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" t="s">
+        <v>75</v>
+      </c>
+      <c r="E35" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35">
+        <v>6</v>
+      </c>
+      <c r="G35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>3</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" t="s">
+        <v>128</v>
+      </c>
+      <c r="F36">
+        <v>4</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>3</v>
+      </c>
+      <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" t="s">
+        <v>179</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>3</v>
+      </c>
+      <c r="B38">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" t="s">
+        <v>171</v>
+      </c>
+      <c r="E38" t="s">
+        <v>128</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>3</v>
+      </c>
+      <c r="B39">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E39" t="s">
+        <v>128</v>
+      </c>
+      <c r="F39">
+        <v>6</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>3</v>
+      </c>
+      <c r="B40">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" t="s">
+        <v>128</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>3</v>
+      </c>
+      <c r="B41">
+        <v>10</v>
+      </c>
+      <c r="C41" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" t="s">
+        <v>112</v>
+      </c>
+      <c r="E41" t="s">
+        <v>141</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>3</v>
+      </c>
+      <c r="B42">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" t="s">
+        <v>128</v>
+      </c>
+      <c r="F42">
+        <v>18</v>
+      </c>
+      <c r="G42" s="1">
+        <v>-0.56999999999999995</v>
+      </c>
+      <c r="H42" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>3</v>
+      </c>
+      <c r="B43">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" t="s">
+        <v>47</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" t="s">
+        <v>182</v>
+      </c>
+      <c r="E44" t="s">
+        <v>183</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>3</v>
+      </c>
+      <c r="B45">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>93</v>
+      </c>
+      <c r="D45" t="s">
+        <v>56</v>
+      </c>
+      <c r="E45" t="s">
+        <v>128</v>
+      </c>
+      <c r="F45">
+        <v>3</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>3</v>
+      </c>
+      <c r="B46">
+        <v>15</v>
+      </c>
+      <c r="C46" t="s">
+        <v>94</v>
+      </c>
+      <c r="D46" t="s">
+        <v>63</v>
+      </c>
+      <c r="E46" t="s">
+        <v>128</v>
+      </c>
+      <c r="F46">
+        <v>2</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -5582,7 +7849,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B6E11CD-9E90-4D11-92A8-D8C539D81231}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="29.28515625" customWidth="1"/>
@@ -6313,6 +8580,357 @@
         <v>0</v>
       </c>
       <c r="G31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" t="s">
+        <v>54</v>
+      </c>
+      <c r="E32" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32">
+        <v>6</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" t="s">
+        <v>171</v>
+      </c>
+      <c r="E33" t="s">
+        <v>128</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>3</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" t="s">
+        <v>128</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" t="s">
+        <v>54</v>
+      </c>
+      <c r="E35" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35">
+        <v>8</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>3</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" t="s">
+        <v>128</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>3</v>
+      </c>
+      <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" t="s">
+        <v>63</v>
+      </c>
+      <c r="E37" t="s">
+        <v>133</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>3</v>
+      </c>
+      <c r="B38">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>152</v>
+      </c>
+      <c r="D38" t="s">
+        <v>60</v>
+      </c>
+      <c r="E38" t="s">
+        <v>128</v>
+      </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="G38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>3</v>
+      </c>
+      <c r="B39">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39" t="s">
+        <v>128</v>
+      </c>
+      <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>3</v>
+      </c>
+      <c r="B40">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" t="s">
+        <v>128</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>3</v>
+      </c>
+      <c r="B41">
+        <v>10</v>
+      </c>
+      <c r="C41" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" t="s">
+        <v>112</v>
+      </c>
+      <c r="E41" t="s">
+        <v>141</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>3</v>
+      </c>
+      <c r="B42">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" t="s">
+        <v>128</v>
+      </c>
+      <c r="F42">
+        <v>27</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H42" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>3</v>
+      </c>
+      <c r="B43">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>96</v>
+      </c>
+      <c r="D43" t="s">
+        <v>175</v>
+      </c>
+      <c r="E43" t="s">
+        <v>47</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
+        <v>74</v>
+      </c>
+      <c r="D44" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" t="s">
+        <v>128</v>
+      </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
+      <c r="G44" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>3</v>
+      </c>
+      <c r="B45">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" t="s">
+        <v>46</v>
+      </c>
+      <c r="E45" t="s">
+        <v>128</v>
+      </c>
+      <c r="F45">
+        <v>4</v>
+      </c>
+      <c r="G45" s="1">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>3</v>
+      </c>
+      <c r="B46">
+        <v>15</v>
+      </c>
+      <c r="C46" t="s">
+        <v>62</v>
+      </c>
+      <c r="D46" t="s">
+        <v>175</v>
+      </c>
+      <c r="E46" t="s">
+        <v>128</v>
+      </c>
+      <c r="F46">
+        <v>3</v>
+      </c>
+      <c r="G46" s="1">
         <v>0</v>
       </c>
     </row>
@@ -6326,7 +8944,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222824F9-1AC4-4931-8973-86755A3F1C37}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7055,6 +9673,357 @@
       </c>
       <c r="G31" s="1">
         <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" t="s">
+        <v>171</v>
+      </c>
+      <c r="E32" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32">
+        <v>3</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" t="s">
+        <v>171</v>
+      </c>
+      <c r="E33" t="s">
+        <v>172</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>3</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>97</v>
+      </c>
+      <c r="D34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" t="s">
+        <v>184</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" t="s">
+        <v>60</v>
+      </c>
+      <c r="E35" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35">
+        <v>7</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>3</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>173</v>
+      </c>
+      <c r="D36" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" t="s">
+        <v>174</v>
+      </c>
+      <c r="F36">
+        <v>3</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>3</v>
+      </c>
+      <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" t="s">
+        <v>128</v>
+      </c>
+      <c r="F37">
+        <v>2</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>3</v>
+      </c>
+      <c r="B38">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" t="s">
+        <v>63</v>
+      </c>
+      <c r="E38" t="s">
+        <v>133</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>3</v>
+      </c>
+      <c r="B39">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" t="s">
+        <v>128</v>
+      </c>
+      <c r="F39">
+        <v>2</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>3</v>
+      </c>
+      <c r="B40">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>100</v>
+      </c>
+      <c r="D40" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" t="s">
+        <v>128</v>
+      </c>
+      <c r="F40">
+        <v>8</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>3</v>
+      </c>
+      <c r="B41">
+        <v>10</v>
+      </c>
+      <c r="C41" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E41" t="s">
+        <v>128</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>3</v>
+      </c>
+      <c r="B42">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" t="s">
+        <v>128</v>
+      </c>
+      <c r="F42">
+        <v>27</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H42" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>3</v>
+      </c>
+      <c r="B43">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>96</v>
+      </c>
+      <c r="D43" t="s">
+        <v>175</v>
+      </c>
+      <c r="E43" t="s">
+        <v>47</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
+        <v>74</v>
+      </c>
+      <c r="D44" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" t="s">
+        <v>128</v>
+      </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
+      <c r="G44" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>3</v>
+      </c>
+      <c r="B45">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>77</v>
+      </c>
+      <c r="D45" t="s">
+        <v>178</v>
+      </c>
+      <c r="E45" t="s">
+        <v>128</v>
+      </c>
+      <c r="F45">
+        <v>3</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>3</v>
+      </c>
+      <c r="B46">
+        <v>15</v>
+      </c>
+      <c r="C46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" t="s">
+        <v>171</v>
+      </c>
+      <c r="E46" t="s">
+        <v>128</v>
+      </c>
+      <c r="F46">
+        <v>4</v>
+      </c>
+      <c r="G46" s="1">
+        <v>-0.28999999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -7067,7 +10036,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB542D51-1B6E-4A6F-B385-F419919DC470}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="35.85546875" bestFit="1" customWidth="1"/>
@@ -7798,6 +10767,357 @@
         <v>2</v>
       </c>
       <c r="G31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" t="s">
+        <v>128</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33" t="s">
+        <v>128</v>
+      </c>
+      <c r="F33">
+        <v>5</v>
+      </c>
+      <c r="G33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>3</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" t="s">
+        <v>128</v>
+      </c>
+      <c r="F34">
+        <v>8</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" t="s">
+        <v>171</v>
+      </c>
+      <c r="E35" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35">
+        <v>4</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>3</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" t="s">
+        <v>128</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H36" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>3</v>
+      </c>
+      <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" t="s">
+        <v>128</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>3</v>
+      </c>
+      <c r="B38">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" t="s">
+        <v>128</v>
+      </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>3</v>
+      </c>
+      <c r="B39">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>100</v>
+      </c>
+      <c r="D39" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" t="s">
+        <v>128</v>
+      </c>
+      <c r="F39">
+        <v>8</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>3</v>
+      </c>
+      <c r="B40">
+        <v>9</v>
+      </c>
+      <c r="C40" t="s">
+        <v>49</v>
+      </c>
+      <c r="D40" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" t="s">
+        <v>128</v>
+      </c>
+      <c r="F40">
+        <v>27</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H40" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>3</v>
+      </c>
+      <c r="B41">
+        <v>10</v>
+      </c>
+      <c r="C41" t="s">
+        <v>105</v>
+      </c>
+      <c r="D41" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" t="s">
+        <v>185</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>3</v>
+      </c>
+      <c r="B42">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" t="s">
+        <v>78</v>
+      </c>
+      <c r="E42" t="s">
+        <v>128</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>3</v>
+      </c>
+      <c r="B43">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" t="s">
+        <v>128</v>
+      </c>
+      <c r="F43">
+        <v>6</v>
+      </c>
+      <c r="G43" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44" t="s">
+        <v>46</v>
+      </c>
+      <c r="E44" t="s">
+        <v>128</v>
+      </c>
+      <c r="F44">
+        <v>4</v>
+      </c>
+      <c r="G44" s="1">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>3</v>
+      </c>
+      <c r="B45">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>106</v>
+      </c>
+      <c r="D45" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" t="s">
+        <v>186</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>3</v>
+      </c>
+      <c r="B46">
+        <v>15</v>
+      </c>
+      <c r="C46" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" t="s">
+        <v>175</v>
+      </c>
+      <c r="E46" t="s">
+        <v>128</v>
+      </c>
+      <c r="F46">
+        <v>3</v>
+      </c>
+      <c r="G46" s="1">
         <v>0</v>
       </c>
     </row>

--- a/data/season_26_27.xlsx
+++ b/data/season_26_27.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lukec\OneDrive\Documents\Rprojects\misc_projects\fpl_r\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE83DAF2-574A-4275-ADB7-710CB65DBB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D517CD-0862-4077-83BA-8A41C55E74B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="842" activeTab="9" xr2:uid="{782628A8-4822-4E84-B9D1-9E9F8CA74FCB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="842" xr2:uid="{782628A8-4822-4E84-B9D1-9E9F8CA74FCB}"/>
   </bookViews>
   <sheets>
     <sheet name="season" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="232">
   <si>
     <t>gameweek_id</t>
   </si>
@@ -614,12 +614,132 @@
   </si>
   <si>
     <t xml:space="preserve">Tarkowski </t>
+  </si>
+  <si>
+    <t>Ndiaye</t>
+  </si>
+  <si>
+    <t>Rogers</t>
+  </si>
+  <si>
+    <t>Brobbey</t>
+  </si>
+  <si>
+    <t>Simms</t>
+  </si>
+  <si>
+    <t>Raya</t>
+  </si>
+  <si>
+    <t>Igor Jesus</t>
+  </si>
+  <si>
+    <t>Wissa</t>
+  </si>
+  <si>
+    <t>Shaw</t>
+  </si>
+  <si>
+    <t>De Cuyper</t>
+  </si>
+  <si>
+    <t>Gabriel</t>
+  </si>
+  <si>
+    <t>Calafiori</t>
+  </si>
+  <si>
+    <t>Gibbs-White</t>
+  </si>
+  <si>
+    <t>Palmer</t>
+  </si>
+  <si>
+    <t>amy</t>
+  </si>
+  <si>
+    <t>Mosquera</t>
+  </si>
+  <si>
+    <t>Hall</t>
+  </si>
+  <si>
+    <t>Wirtz</t>
+  </si>
+  <si>
+    <t>Barry</t>
+  </si>
+  <si>
+    <t>jamesc</t>
+  </si>
+  <si>
+    <t>SUN (A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muharemović </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rogers </t>
+  </si>
+  <si>
+    <t>COV (A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Button </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barry </t>
+  </si>
+  <si>
+    <t>TOT (A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Botman </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mendy lens error </t>
+  </si>
+  <si>
+    <t>Done (58)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hall </t>
+  </si>
+  <si>
+    <t>EVE (H)</t>
+  </si>
+  <si>
+    <t>Done (80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaw lens error </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simms </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Röhl keyboard_arrow_down </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maguire keyboard_arrow_up </t>
+  </si>
+  <si>
+    <t xml:space="preserve">De Cuyper </t>
+  </si>
+  <si>
+    <t>Done (19)</t>
+  </si>
+  <si>
+    <t>Done (13)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -649,62 +769,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="15">
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <numFmt numFmtId="166" formatCode="#,##0.0"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
       <fill>
@@ -865,12 +946,6 @@
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -885,16 +960,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}" name="Table1" displayName="Table1" ref="A1:J25" totalsRowShown="0">
-  <autoFilter ref="A1:J25" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}" name="Table1" displayName="Table1" ref="A1:J33" totalsRowShown="0">
+  <autoFilter ref="A1:J33" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{3DFDA157-BD05-4F91-BBC2-46C272CA2753}" name="date"/>
     <tableColumn id="2" xr3:uid="{E77E158C-7AE3-4435-9E81-D58EA8264AE1}" name="gameweek_id"/>
     <tableColumn id="3" xr3:uid="{4EC2B4AA-BB48-4F1C-AA23-865B4955D775}" name="season_standing"/>
     <tableColumn id="4" xr3:uid="{1A5CC8A7-E0BF-4423-9565-863589D0157E}" name="team"/>
-    <tableColumn id="5" xr3:uid="{7F46AE02-3FA0-4946-9C0E-9C4075370946}" name="season_transfers" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{CD26F816-00C7-4F1F-B5FB-E9B2D89B04C7}" name="overall_rank" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{4035F136-3D22-4E3D-951A-6F27496E67CD}" name="team_value" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{7F46AE02-3FA0-4946-9C0E-9C4075370946}" name="season_transfers" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{CD26F816-00C7-4F1F-B5FB-E9B2D89B04C7}" name="overall_rank" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{4035F136-3D22-4E3D-951A-6F27496E67CD}" name="team_value" dataDxfId="0"/>
     <tableColumn id="8" xr3:uid="{873B883E-CCA1-4415-9B58-AC7C5BD906B9}" name="gw_net"/>
     <tableColumn id="9" xr3:uid="{C348C7FD-EAB4-47B7-9C3E-0CF639A77318}" name="total"/>
     <tableColumn id="10" xr3:uid="{29219B07-DFC0-4696-B9A2-8E2F83EBFA88}" name="chip"/>
@@ -904,8 +979,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}" name="tim" displayName="tim" ref="A1:H46" totalsRowShown="0">
-  <autoFilter ref="A1:H46" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}" name="tim" displayName="tim" ref="A1:H61" totalsRowShown="0">
+  <autoFilter ref="A1:H61" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{67AFB369-C03A-462B-972F-AF60CDE2CFAB}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{44789776-FE7D-494A-B94B-2A601E85CB98}" name="player_slot"/>
@@ -921,8 +996,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}" name="Table6" displayName="Table6" ref="A1:G9" totalsRowShown="0">
-  <autoFilter ref="A1:G9" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}" name="Table6" displayName="Table6" ref="A1:G19" totalsRowShown="0">
+  <autoFilter ref="A1:G19" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G2">
     <sortCondition ref="A1:A2"/>
   </sortState>
@@ -940,8 +1015,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}" name="luke" displayName="luke" ref="A1:H46" totalsRowShown="0">
-  <autoFilter ref="A1:H46" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}" name="luke" displayName="luke" ref="A1:H61" totalsRowShown="0">
+  <autoFilter ref="A1:H61" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{E03C2832-F763-487D-BAF0-A846252C195D}" name="gameweek_id"/>
     <tableColumn id="7" xr3:uid="{442DEA06-1307-4EEB-981E-C530D39C1221}" name="player_slot"/>
@@ -957,8 +1032,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}" name="james_c" displayName="james_c" ref="A1:H46" totalsRowShown="0">
-  <autoFilter ref="A1:H46" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}" name="james_c" displayName="james_c" ref="A1:H61" totalsRowShown="0">
+  <autoFilter ref="A1:H61" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{E3512878-F631-4A83-9CF0-34024519F60B}" name="gameweek_id"/>
     <tableColumn id="7" xr3:uid="{FB753C77-F849-4945-8ED7-323A572ADEC0}" name="player_slot"/>
@@ -974,8 +1049,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}" name="james_lm" displayName="james_lm" ref="A1:H46" totalsRowShown="0">
-  <autoFilter ref="A1:H46" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}" name="james_lm" displayName="james_lm" ref="A1:H61" totalsRowShown="0">
+  <autoFilter ref="A1:H61" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{85A61EA9-7D32-46E4-A518-261A47E355F4}" name="gameweek_id"/>
     <tableColumn id="7" xr3:uid="{86687FAE-12A2-4491-A6A8-B516A188A202}" name="player_slot"/>
@@ -991,8 +1066,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}" name="fred" displayName="fred" ref="A1:H46" totalsRowShown="0">
-  <autoFilter ref="A1:H46" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}" name="fred" displayName="fred" ref="A1:H61" totalsRowShown="0">
+  <autoFilter ref="A1:H61" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{BD2A7E80-7899-44F4-A0E0-E1951D803BBF}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{9A789C6B-DF65-4741-842B-32F8E097183F}" name="player_slot"/>
@@ -1008,8 +1083,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}" name="amy" displayName="amy" ref="A1:H46" totalsRowShown="0">
-  <autoFilter ref="A1:H46" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}" name="amy" displayName="amy" ref="A1:H61" totalsRowShown="0">
+  <autoFilter ref="A1:H61" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{3EEC9588-A154-4394-B1C6-FB872F361A10}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{CFDBEB1B-AC4B-4140-B9D5-FB0F16BBFA70}" name="player_slot"/>
@@ -1025,8 +1100,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}" name="andy" displayName="andy" ref="A1:H46" totalsRowShown="0">
-  <autoFilter ref="A1:H46" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}" name="andy" displayName="andy" ref="A1:H61" totalsRowShown="0">
+  <autoFilter ref="A1:H61" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{25B33829-3E10-4EA1-9ED1-D911F47A3168}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{4C06A930-A949-45AD-BF12-6F05B56443BE}" name="player_slot"/>
@@ -1042,8 +1117,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}" name="lewis" displayName="lewis" ref="A1:H46" totalsRowShown="0">
-  <autoFilter ref="A1:H46" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}" name="lewis" displayName="lewis" ref="A1:H61" totalsRowShown="0">
+  <autoFilter ref="A1:H61" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{14461CE9-1F87-4E76-B041-83CB47DED671}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{0AAB3767-3503-40AA-A974-A7C448E60023}" name="player_slot"/>
@@ -1417,9 +1492,9 @@
         <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>933078</v>
-      </c>
-      <c r="G2" s="2">
+        <v>1142767</v>
+      </c>
+      <c r="G2" s="5">
         <v>100</v>
       </c>
       <c r="H2" s="2">
@@ -1449,9 +1524,9 @@
         <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>4021058</v>
-      </c>
-      <c r="G3" s="2">
+        <v>4673927</v>
+      </c>
+      <c r="G3" s="5">
         <v>100</v>
       </c>
       <c r="H3">
@@ -1481,9 +1556,9 @@
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>4296597</v>
-      </c>
-      <c r="G4" s="2">
+        <v>4969899</v>
+      </c>
+      <c r="G4" s="5">
         <v>100</v>
       </c>
       <c r="H4">
@@ -1510,9 +1585,9 @@
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>4591122</v>
-      </c>
-      <c r="G5" s="2">
+        <v>5282775</v>
+      </c>
+      <c r="G5" s="5">
         <v>100</v>
       </c>
       <c r="H5">
@@ -1542,9 +1617,9 @@
         <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>5683502</v>
-      </c>
-      <c r="G6" s="2">
+        <v>6382778</v>
+      </c>
+      <c r="G6" s="5">
         <v>100</v>
       </c>
       <c r="H6">
@@ -1571,9 +1646,9 @@
         <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>5940242</v>
-      </c>
-      <c r="G7" s="2">
+        <v>6633922</v>
+      </c>
+      <c r="G7" s="5">
         <v>100</v>
       </c>
       <c r="H7">
@@ -1600,9 +1675,9 @@
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>6192133</v>
-      </c>
-      <c r="G8" s="2">
+        <v>6875541</v>
+      </c>
+      <c r="G8" s="5">
         <v>100</v>
       </c>
       <c r="H8">
@@ -1629,9 +1704,9 @@
         <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>6868753</v>
-      </c>
-      <c r="G9" s="2">
+        <v>7485068</v>
+      </c>
+      <c r="G9" s="5">
         <v>100</v>
       </c>
       <c r="H9">
@@ -1660,7 +1735,7 @@
       <c r="F10" s="2">
         <v>432791</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="5">
         <v>100.3</v>
       </c>
       <c r="H10">
@@ -1689,7 +1764,7 @@
       <c r="F11" s="2">
         <v>2320860</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="5">
         <v>100.1</v>
       </c>
       <c r="H11">
@@ -1718,7 +1793,7 @@
       <c r="F12" s="2">
         <v>2439660</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="5">
         <v>100.1</v>
       </c>
       <c r="H12">
@@ -1747,7 +1822,7 @@
       <c r="F13" s="2">
         <v>2761818</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="5">
         <v>100.2</v>
       </c>
       <c r="H13">
@@ -1776,7 +1851,7 @@
       <c r="F14" s="2">
         <v>3619481</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="5">
         <v>99.9</v>
       </c>
       <c r="H14">
@@ -1805,7 +1880,7 @@
       <c r="F15" s="2">
         <v>4886627</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="5">
         <v>100.1</v>
       </c>
       <c r="H15">
@@ -1834,7 +1909,7 @@
       <c r="F16" s="2">
         <v>5838676</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="5">
         <v>100.1</v>
       </c>
       <c r="H16">
@@ -1863,7 +1938,7 @@
       <c r="F17" s="2">
         <v>6036188</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="5">
         <v>100.1</v>
       </c>
       <c r="H17">
@@ -1890,9 +1965,9 @@
         <v>2</v>
       </c>
       <c r="F18" s="2">
-        <v>567858</v>
-      </c>
-      <c r="G18" s="2">
+        <v>568295</v>
+      </c>
+      <c r="G18" s="5">
         <v>100.6</v>
       </c>
       <c r="H18">
@@ -1922,9 +1997,9 @@
         <v>1</v>
       </c>
       <c r="F19" s="2">
-        <v>1784329</v>
-      </c>
-      <c r="G19">
+        <v>1783829</v>
+      </c>
+      <c r="G19" s="5">
         <v>100.1</v>
       </c>
       <c r="H19">
@@ -1954,9 +2029,9 @@
         <v>0</v>
       </c>
       <c r="F20" s="2">
-        <v>1982279</v>
-      </c>
-      <c r="G20">
+        <v>1961668</v>
+      </c>
+      <c r="G20" s="5">
         <v>99.9</v>
       </c>
       <c r="H20">
@@ -1986,9 +2061,9 @@
         <v>1</v>
       </c>
       <c r="F21" s="2">
-        <v>2208110</v>
-      </c>
-      <c r="G21">
+        <v>2208735</v>
+      </c>
+      <c r="G21" s="5">
         <v>99.8</v>
       </c>
       <c r="H21">
@@ -2018,9 +2093,9 @@
         <v>3</v>
       </c>
       <c r="F22" s="2">
-        <v>2871860</v>
-      </c>
-      <c r="G22">
+        <v>2872002</v>
+      </c>
+      <c r="G22" s="5">
         <v>100.2</v>
       </c>
       <c r="H22">
@@ -2050,9 +2125,9 @@
         <v>0</v>
       </c>
       <c r="F23" s="2">
-        <v>3523110</v>
-      </c>
-      <c r="G23">
+        <v>3522752</v>
+      </c>
+      <c r="G23" s="5">
         <v>100</v>
       </c>
       <c r="H23">
@@ -2082,9 +2157,9 @@
         <v>0</v>
       </c>
       <c r="F24" s="2">
-        <v>5818110</v>
-      </c>
-      <c r="G24">
+        <v>5817678</v>
+      </c>
+      <c r="G24" s="5">
         <v>100.2</v>
       </c>
       <c r="H24">
@@ -2111,9 +2186,9 @@
         <v>1</v>
       </c>
       <c r="F25" s="2">
-        <v>6084360</v>
-      </c>
-      <c r="G25">
+        <v>6084281</v>
+      </c>
+      <c r="G25" s="5">
         <v>100.7</v>
       </c>
       <c r="H25">
@@ -2126,22 +2201,252 @@
         <v>159</v>
       </c>
     </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>46277</v>
+      </c>
+      <c r="B26">
+        <v>4</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2</v>
+      </c>
+      <c r="F26" s="2">
+        <v>144301</v>
+      </c>
+      <c r="G26" s="5">
+        <v>101</v>
+      </c>
+      <c r="H26">
+        <v>100</v>
+      </c>
+      <c r="I26">
+        <v>322</v>
+      </c>
+      <c r="J26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>46277</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="2">
+        <v>3</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1883400</v>
+      </c>
+      <c r="G27" s="5">
+        <v>100</v>
+      </c>
+      <c r="H27">
+        <v>76</v>
+      </c>
+      <c r="I27">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>46277</v>
+      </c>
+      <c r="B28">
+        <v>4</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="2">
+        <v>3</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1883400</v>
+      </c>
+      <c r="G28" s="5">
+        <v>99.7</v>
+      </c>
+      <c r="H28">
+        <v>80</v>
+      </c>
+      <c r="I28">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>46277</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="2">
+        <v>3</v>
+      </c>
+      <c r="F29" s="2">
+        <v>2002200</v>
+      </c>
+      <c r="G29" s="5">
+        <v>100.7</v>
+      </c>
+      <c r="H29">
+        <v>84</v>
+      </c>
+      <c r="I29">
+        <v>280</v>
+      </c>
+      <c r="J29" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>46277</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
+      <c r="C30">
+        <v>5</v>
+      </c>
+      <c r="D30" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="2">
+        <v>3</v>
+      </c>
+      <c r="F30" s="2">
+        <v>2536200</v>
+      </c>
+      <c r="G30" s="5">
+        <v>99.6</v>
+      </c>
+      <c r="H30">
+        <v>70</v>
+      </c>
+      <c r="I30">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>46277</v>
+      </c>
+      <c r="B31">
+        <v>4</v>
+      </c>
+      <c r="C31">
+        <v>6</v>
+      </c>
+      <c r="D31" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" s="2">
+        <v>3</v>
+      </c>
+      <c r="F31" s="2">
+        <v>3362987</v>
+      </c>
+      <c r="G31" s="5">
+        <v>99.7</v>
+      </c>
+      <c r="H31">
+        <v>74</v>
+      </c>
+      <c r="I31">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>46277</v>
+      </c>
+      <c r="B32">
+        <v>4</v>
+      </c>
+      <c r="C32">
+        <v>7</v>
+      </c>
+      <c r="D32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>4391175</v>
+      </c>
+      <c r="G32" s="5">
+        <v>101.3</v>
+      </c>
+      <c r="H32">
+        <v>83</v>
+      </c>
+      <c r="I32">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>46277</v>
+      </c>
+      <c r="B33">
+        <v>4</v>
+      </c>
+      <c r="C33">
+        <v>8</v>
+      </c>
+      <c r="D33" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2">
+        <v>4471175</v>
+      </c>
+      <c r="G33" s="5">
+        <v>99.7</v>
+      </c>
+      <c r="H33">
+        <v>80</v>
+      </c>
+      <c r="I33">
+        <v>252</v>
+      </c>
+    </row>
     <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <conditionalFormatting sqref="A2:J25">
-    <cfRule type="expression" dxfId="3" priority="5">
+  <conditionalFormatting sqref="A2:J33">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>MOD($B2, 2) = 1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="6">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>MOD($B2, 2) = 0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18:C25">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>MOD($B18, 2) = 1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>MOD($B18, 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2153,7 +2458,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A820DAB-6033-4E1A-86E6-3C9D8203F219}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3232,6 +3537,357 @@
         <v>3</v>
       </c>
       <c r="G46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>4</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47" t="s">
+        <v>212</v>
+      </c>
+      <c r="E47" t="s">
+        <v>128</v>
+      </c>
+      <c r="F47">
+        <v>14</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="H47" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>4</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>188</v>
+      </c>
+      <c r="D48" t="s">
+        <v>140</v>
+      </c>
+      <c r="E48" t="s">
+        <v>128</v>
+      </c>
+      <c r="F48">
+        <v>11</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>4</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
+      </c>
+      <c r="C49" t="s">
+        <v>192</v>
+      </c>
+      <c r="D49" t="s">
+        <v>218</v>
+      </c>
+      <c r="E49" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49">
+        <v>8</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>4</v>
+      </c>
+      <c r="B50">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>35</v>
+      </c>
+      <c r="D50" t="s">
+        <v>212</v>
+      </c>
+      <c r="E50" t="s">
+        <v>128</v>
+      </c>
+      <c r="F50">
+        <v>6</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>4</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" t="s">
+        <v>212</v>
+      </c>
+      <c r="E51" t="s">
+        <v>224</v>
+      </c>
+      <c r="F51">
+        <v>3</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>4</v>
+      </c>
+      <c r="B52">
+        <v>6</v>
+      </c>
+      <c r="C52" t="s">
+        <v>173</v>
+      </c>
+      <c r="D52" t="s">
+        <v>140</v>
+      </c>
+      <c r="E52" t="s">
+        <v>133</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>4</v>
+      </c>
+      <c r="B53">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>84</v>
+      </c>
+      <c r="D53" t="s">
+        <v>215</v>
+      </c>
+      <c r="E53" t="s">
+        <v>128</v>
+      </c>
+      <c r="F53">
+        <v>17</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>4</v>
+      </c>
+      <c r="B54">
+        <v>8</v>
+      </c>
+      <c r="C54" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" t="s">
+        <v>156</v>
+      </c>
+      <c r="E54" t="s">
+        <v>128</v>
+      </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>4</v>
+      </c>
+      <c r="B55">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>96</v>
+      </c>
+      <c r="D55" t="s">
+        <v>143</v>
+      </c>
+      <c r="E55" t="s">
+        <v>128</v>
+      </c>
+      <c r="F55">
+        <v>5</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>4</v>
+      </c>
+      <c r="B56">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>51</v>
+      </c>
+      <c r="D56" t="s">
+        <v>143</v>
+      </c>
+      <c r="E56" t="s">
+        <v>128</v>
+      </c>
+      <c r="F56">
+        <v>12</v>
+      </c>
+      <c r="G56" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>4</v>
+      </c>
+      <c r="B57">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>101</v>
+      </c>
+      <c r="D57" t="s">
+        <v>144</v>
+      </c>
+      <c r="E57" t="s">
+        <v>128</v>
+      </c>
+      <c r="F57">
+        <v>4</v>
+      </c>
+      <c r="G57" s="1">
+        <v>2</v>
+      </c>
+      <c r="H57" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>4</v>
+      </c>
+      <c r="B58">
+        <v>12</v>
+      </c>
+      <c r="C58" t="s">
+        <v>187</v>
+      </c>
+      <c r="D58" t="s">
+        <v>138</v>
+      </c>
+      <c r="E58" t="s">
+        <v>128</v>
+      </c>
+      <c r="F58">
+        <v>2</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>4</v>
+      </c>
+      <c r="B59">
+        <v>13</v>
+      </c>
+      <c r="C59" t="s">
+        <v>191</v>
+      </c>
+      <c r="D59" t="s">
+        <v>150</v>
+      </c>
+      <c r="E59" t="s">
+        <v>230</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>4</v>
+      </c>
+      <c r="B60">
+        <v>14</v>
+      </c>
+      <c r="C60" t="s">
+        <v>190</v>
+      </c>
+      <c r="D60" t="s">
+        <v>134</v>
+      </c>
+      <c r="E60" t="s">
+        <v>128</v>
+      </c>
+      <c r="F60">
+        <v>2</v>
+      </c>
+      <c r="G60" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>4</v>
+      </c>
+      <c r="B61">
+        <v>15</v>
+      </c>
+      <c r="C61" t="s">
+        <v>189</v>
+      </c>
+      <c r="D61" t="s">
+        <v>138</v>
+      </c>
+      <c r="E61" t="s">
+        <v>128</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3254,7 +3910,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330229B3-0B25-4B18-9D20-120CB711B0FB}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -3446,6 +4102,206 @@
         <v>1</v>
       </c>
     </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" t="s">
+        <v>193</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>194</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" t="s">
+        <v>195</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>196</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>197</v>
+      </c>
+      <c r="G12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>167</v>
+      </c>
+      <c r="C13" t="s">
+        <v>198</v>
+      </c>
+      <c r="D13">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>199</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>206</v>
+      </c>
+      <c r="C14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="s">
+        <v>201</v>
+      </c>
+      <c r="G14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>206</v>
+      </c>
+      <c r="C15" t="s">
+        <v>202</v>
+      </c>
+      <c r="D15">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>203</v>
+      </c>
+      <c r="G15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>206</v>
+      </c>
+      <c r="C16" t="s">
+        <v>204</v>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>205</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>211</v>
+      </c>
+      <c r="C17" t="s">
+        <v>207</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="F17" t="s">
+        <v>208</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>211</v>
+      </c>
+      <c r="C18" t="s">
+        <v>209</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="F18" t="s">
+        <v>194</v>
+      </c>
+      <c r="G18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>211</v>
+      </c>
+      <c r="C19" t="s">
+        <v>195</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>210</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -3456,7 +4312,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BFE37CD-4558-41F4-92EA-FE7453319710}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -4545,6 +5401,357 @@
         <v>0</v>
       </c>
     </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>4</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47" t="s">
+        <v>212</v>
+      </c>
+      <c r="E47" t="s">
+        <v>128</v>
+      </c>
+      <c r="F47" s="3">
+        <v>14</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>4</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" t="s">
+        <v>212</v>
+      </c>
+      <c r="E48" t="s">
+        <v>128</v>
+      </c>
+      <c r="F48" s="3">
+        <v>6</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>4</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
+      </c>
+      <c r="C49" t="s">
+        <v>79</v>
+      </c>
+      <c r="D49" t="s">
+        <v>212</v>
+      </c>
+      <c r="E49" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49" s="3">
+        <v>6</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>4</v>
+      </c>
+      <c r="B50">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>213</v>
+      </c>
+      <c r="D50" t="s">
+        <v>127</v>
+      </c>
+      <c r="E50" t="s">
+        <v>128</v>
+      </c>
+      <c r="F50" s="3">
+        <v>7</v>
+      </c>
+      <c r="G50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>4</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>214</v>
+      </c>
+      <c r="D51" t="s">
+        <v>143</v>
+      </c>
+      <c r="E51" t="s">
+        <v>128</v>
+      </c>
+      <c r="F51" s="3">
+        <v>8</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>4</v>
+      </c>
+      <c r="B52">
+        <v>6</v>
+      </c>
+      <c r="C52" t="s">
+        <v>96</v>
+      </c>
+      <c r="D52" t="s">
+        <v>143</v>
+      </c>
+      <c r="E52" t="s">
+        <v>128</v>
+      </c>
+      <c r="F52" s="3">
+        <v>10</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="H52" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>4</v>
+      </c>
+      <c r="B53">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>84</v>
+      </c>
+      <c r="D53" t="s">
+        <v>215</v>
+      </c>
+      <c r="E53" t="s">
+        <v>128</v>
+      </c>
+      <c r="F53" s="3">
+        <v>17</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>4</v>
+      </c>
+      <c r="B54">
+        <v>8</v>
+      </c>
+      <c r="C54" t="s">
+        <v>81</v>
+      </c>
+      <c r="D54" t="s">
+        <v>144</v>
+      </c>
+      <c r="E54" t="s">
+        <v>128</v>
+      </c>
+      <c r="F54" s="3">
+        <v>3</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>4</v>
+      </c>
+      <c r="B55">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>152</v>
+      </c>
+      <c r="D55" t="s">
+        <v>129</v>
+      </c>
+      <c r="E55" t="s">
+        <v>128</v>
+      </c>
+      <c r="F55" s="3">
+        <v>8</v>
+      </c>
+      <c r="G55" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>4</v>
+      </c>
+      <c r="B56">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>51</v>
+      </c>
+      <c r="D56" t="s">
+        <v>143</v>
+      </c>
+      <c r="E56" t="s">
+        <v>128</v>
+      </c>
+      <c r="F56" s="3">
+        <v>12</v>
+      </c>
+      <c r="G56" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="H56" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>4</v>
+      </c>
+      <c r="B57">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>49</v>
+      </c>
+      <c r="D57" t="s">
+        <v>140</v>
+      </c>
+      <c r="E57" t="s">
+        <v>128</v>
+      </c>
+      <c r="F57" s="3">
+        <v>9</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>4</v>
+      </c>
+      <c r="B58">
+        <v>12</v>
+      </c>
+      <c r="C58" t="s">
+        <v>216</v>
+      </c>
+      <c r="D58" t="s">
+        <v>135</v>
+      </c>
+      <c r="E58" t="s">
+        <v>47</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>4</v>
+      </c>
+      <c r="B59">
+        <v>13</v>
+      </c>
+      <c r="C59" t="s">
+        <v>217</v>
+      </c>
+      <c r="D59" t="s">
+        <v>218</v>
+      </c>
+      <c r="E59" t="s">
+        <v>128</v>
+      </c>
+      <c r="F59" s="3">
+        <v>2</v>
+      </c>
+      <c r="G59" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>4</v>
+      </c>
+      <c r="B60">
+        <v>14</v>
+      </c>
+      <c r="C60" t="s">
+        <v>219</v>
+      </c>
+      <c r="D60" t="s">
+        <v>134</v>
+      </c>
+      <c r="E60" t="s">
+        <v>128</v>
+      </c>
+      <c r="F60" s="3">
+        <v>2</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>4</v>
+      </c>
+      <c r="B61">
+        <v>15</v>
+      </c>
+      <c r="C61" t="s">
+        <v>220</v>
+      </c>
+      <c r="D61" t="s">
+        <v>138</v>
+      </c>
+      <c r="E61" t="s">
+        <v>221</v>
+      </c>
+      <c r="F61" s="3">
+        <v>1</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4556,7 +5763,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A36F238-E413-4105-953D-9BEAF6AEF0DC}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
@@ -5640,6 +6847,357 @@
         <v>3</v>
       </c>
       <c r="G46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>4</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" t="s">
+        <v>215</v>
+      </c>
+      <c r="E47" t="s">
+        <v>128</v>
+      </c>
+      <c r="F47" s="3">
+        <v>8</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>4</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" t="s">
+        <v>212</v>
+      </c>
+      <c r="E48" t="s">
+        <v>128</v>
+      </c>
+      <c r="F48" s="3">
+        <v>6</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>4</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
+      </c>
+      <c r="C49" t="s">
+        <v>222</v>
+      </c>
+      <c r="D49" t="s">
+        <v>134</v>
+      </c>
+      <c r="E49" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>4</v>
+      </c>
+      <c r="B50">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" t="s">
+        <v>223</v>
+      </c>
+      <c r="E50" t="s">
+        <v>128</v>
+      </c>
+      <c r="F50" s="3">
+        <v>8</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>4</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" t="s">
+        <v>212</v>
+      </c>
+      <c r="E51" t="s">
+        <v>224</v>
+      </c>
+      <c r="F51" s="3">
+        <v>3</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>4</v>
+      </c>
+      <c r="B52">
+        <v>6</v>
+      </c>
+      <c r="C52" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" t="s">
+        <v>156</v>
+      </c>
+      <c r="E52" t="s">
+        <v>128</v>
+      </c>
+      <c r="F52" s="3">
+        <v>2</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>4</v>
+      </c>
+      <c r="B53">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>214</v>
+      </c>
+      <c r="D53" t="s">
+        <v>143</v>
+      </c>
+      <c r="E53" t="s">
+        <v>128</v>
+      </c>
+      <c r="F53" s="3">
+        <v>8</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>4</v>
+      </c>
+      <c r="B54">
+        <v>8</v>
+      </c>
+      <c r="C54" t="s">
+        <v>59</v>
+      </c>
+      <c r="D54" t="s">
+        <v>150</v>
+      </c>
+      <c r="E54" t="s">
+        <v>128</v>
+      </c>
+      <c r="F54" s="3">
+        <v>4</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>4</v>
+      </c>
+      <c r="B55">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>51</v>
+      </c>
+      <c r="D55" t="s">
+        <v>143</v>
+      </c>
+      <c r="E55" t="s">
+        <v>128</v>
+      </c>
+      <c r="F55" s="3">
+        <v>24</v>
+      </c>
+      <c r="G55" s="1">
+        <v>1</v>
+      </c>
+      <c r="H55" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>4</v>
+      </c>
+      <c r="B56">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>49</v>
+      </c>
+      <c r="D56" t="s">
+        <v>140</v>
+      </c>
+      <c r="E56" t="s">
+        <v>128</v>
+      </c>
+      <c r="F56" s="3">
+        <v>9</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>4</v>
+      </c>
+      <c r="B57">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>217</v>
+      </c>
+      <c r="D57" t="s">
+        <v>218</v>
+      </c>
+      <c r="E57" t="s">
+        <v>128</v>
+      </c>
+      <c r="F57" s="3">
+        <v>2</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>4</v>
+      </c>
+      <c r="B58">
+        <v>12</v>
+      </c>
+      <c r="C58" t="s">
+        <v>66</v>
+      </c>
+      <c r="D58" t="s">
+        <v>156</v>
+      </c>
+      <c r="E58" t="s">
+        <v>128</v>
+      </c>
+      <c r="F58" s="3">
+        <v>2</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>4</v>
+      </c>
+      <c r="B59">
+        <v>13</v>
+      </c>
+      <c r="C59" t="s">
+        <v>147</v>
+      </c>
+      <c r="D59" t="s">
+        <v>140</v>
+      </c>
+      <c r="E59" t="s">
+        <v>128</v>
+      </c>
+      <c r="F59" s="3">
+        <v>5</v>
+      </c>
+      <c r="G59" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>4</v>
+      </c>
+      <c r="B60">
+        <v>14</v>
+      </c>
+      <c r="C60" t="s">
+        <v>77</v>
+      </c>
+      <c r="D60" t="s">
+        <v>136</v>
+      </c>
+      <c r="E60" t="s">
+        <v>128</v>
+      </c>
+      <c r="F60" s="3">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>4</v>
+      </c>
+      <c r="B61">
+        <v>15</v>
+      </c>
+      <c r="C61" t="s">
+        <v>225</v>
+      </c>
+      <c r="D61" t="s">
+        <v>156</v>
+      </c>
+      <c r="E61" t="s">
+        <v>47</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
         <v>0</v>
       </c>
     </row>
@@ -5653,7 +7211,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0779779-8AAD-4A05-B64B-AAE55E86E147}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
@@ -6737,6 +8295,357 @@
         <v>4</v>
       </c>
       <c r="G46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>4</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" t="s">
+        <v>215</v>
+      </c>
+      <c r="E47" t="s">
+        <v>128</v>
+      </c>
+      <c r="F47" s="3">
+        <v>8</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>4</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" t="s">
+        <v>212</v>
+      </c>
+      <c r="E48" t="s">
+        <v>128</v>
+      </c>
+      <c r="F48" s="3">
+        <v>6</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>4</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
+      </c>
+      <c r="C49" t="s">
+        <v>87</v>
+      </c>
+      <c r="D49" t="s">
+        <v>136</v>
+      </c>
+      <c r="E49" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>4</v>
+      </c>
+      <c r="B50">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50" t="s">
+        <v>129</v>
+      </c>
+      <c r="E50" t="s">
+        <v>128</v>
+      </c>
+      <c r="F50" s="3">
+        <v>2</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>4</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>44</v>
+      </c>
+      <c r="D51" t="s">
+        <v>156</v>
+      </c>
+      <c r="E51" t="s">
+        <v>128</v>
+      </c>
+      <c r="F51" s="3">
+        <v>2</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>4</v>
+      </c>
+      <c r="B52">
+        <v>6</v>
+      </c>
+      <c r="C52" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" t="s">
+        <v>140</v>
+      </c>
+      <c r="E52" t="s">
+        <v>128</v>
+      </c>
+      <c r="F52" s="3">
+        <v>3</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>4</v>
+      </c>
+      <c r="B53">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>81</v>
+      </c>
+      <c r="D53" t="s">
+        <v>144</v>
+      </c>
+      <c r="E53" t="s">
+        <v>128</v>
+      </c>
+      <c r="F53" s="3">
+        <v>3</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>4</v>
+      </c>
+      <c r="B54">
+        <v>8</v>
+      </c>
+      <c r="C54" t="s">
+        <v>214</v>
+      </c>
+      <c r="D54" t="s">
+        <v>143</v>
+      </c>
+      <c r="E54" t="s">
+        <v>128</v>
+      </c>
+      <c r="F54" s="3">
+        <v>16</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="H54" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>4</v>
+      </c>
+      <c r="B55">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>84</v>
+      </c>
+      <c r="D55" t="s">
+        <v>215</v>
+      </c>
+      <c r="E55" t="s">
+        <v>128</v>
+      </c>
+      <c r="F55" s="3">
+        <v>17</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>4</v>
+      </c>
+      <c r="B56">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" t="s">
+        <v>127</v>
+      </c>
+      <c r="E56" t="s">
+        <v>149</v>
+      </c>
+      <c r="F56" s="3">
+        <v>10</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>4</v>
+      </c>
+      <c r="B57">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>49</v>
+      </c>
+      <c r="D57" t="s">
+        <v>140</v>
+      </c>
+      <c r="E57" t="s">
+        <v>128</v>
+      </c>
+      <c r="F57" s="3">
+        <v>9</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>4</v>
+      </c>
+      <c r="B58">
+        <v>12</v>
+      </c>
+      <c r="C58" t="s">
+        <v>180</v>
+      </c>
+      <c r="D58" t="s">
+        <v>139</v>
+      </c>
+      <c r="E58" t="s">
+        <v>128</v>
+      </c>
+      <c r="F58" s="3">
+        <v>9</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>4</v>
+      </c>
+      <c r="B59">
+        <v>13</v>
+      </c>
+      <c r="C59" t="s">
+        <v>226</v>
+      </c>
+      <c r="D59" t="s">
+        <v>136</v>
+      </c>
+      <c r="E59" t="s">
+        <v>47</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>4</v>
+      </c>
+      <c r="B60">
+        <v>14</v>
+      </c>
+      <c r="C60" t="s">
+        <v>225</v>
+      </c>
+      <c r="D60" t="s">
+        <v>156</v>
+      </c>
+      <c r="E60" t="s">
+        <v>47</v>
+      </c>
+      <c r="F60" s="3">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>4</v>
+      </c>
+      <c r="B61">
+        <v>15</v>
+      </c>
+      <c r="C61" t="s">
+        <v>85</v>
+      </c>
+      <c r="D61" t="s">
+        <v>157</v>
+      </c>
+      <c r="E61" t="s">
+        <v>47</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
         <v>0</v>
       </c>
     </row>
@@ -6750,7 +8659,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{079AB974-BCF6-45DE-BAD2-52D6AC42558C}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -7839,6 +9748,357 @@
         <v>0</v>
       </c>
     </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>4</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47" t="s">
+        <v>212</v>
+      </c>
+      <c r="E47" t="s">
+        <v>128</v>
+      </c>
+      <c r="F47">
+        <v>14</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>4</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>89</v>
+      </c>
+      <c r="D48" t="s">
+        <v>212</v>
+      </c>
+      <c r="E48" t="s">
+        <v>128</v>
+      </c>
+      <c r="F48">
+        <v>9</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1</v>
+      </c>
+      <c r="H48" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>4</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
+      </c>
+      <c r="C49" t="s">
+        <v>90</v>
+      </c>
+      <c r="D49" t="s">
+        <v>144</v>
+      </c>
+      <c r="E49" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49">
+        <v>8</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>4</v>
+      </c>
+      <c r="B50">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>94</v>
+      </c>
+      <c r="D50" t="s">
+        <v>150</v>
+      </c>
+      <c r="E50" t="s">
+        <v>128</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>4</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>227</v>
+      </c>
+      <c r="D51" t="s">
+        <v>218</v>
+      </c>
+      <c r="E51" t="s">
+        <v>47</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>4</v>
+      </c>
+      <c r="B52">
+        <v>6</v>
+      </c>
+      <c r="C52" t="s">
+        <v>82</v>
+      </c>
+      <c r="D52" t="s">
+        <v>140</v>
+      </c>
+      <c r="E52" t="s">
+        <v>133</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>4</v>
+      </c>
+      <c r="B53">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>70</v>
+      </c>
+      <c r="D53" t="s">
+        <v>212</v>
+      </c>
+      <c r="E53" t="s">
+        <v>224</v>
+      </c>
+      <c r="F53">
+        <v>3</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>4</v>
+      </c>
+      <c r="B54">
+        <v>8</v>
+      </c>
+      <c r="C54" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" t="s">
+        <v>140</v>
+      </c>
+      <c r="E54" t="s">
+        <v>128</v>
+      </c>
+      <c r="F54">
+        <v>3</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>4</v>
+      </c>
+      <c r="B55">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>51</v>
+      </c>
+      <c r="D55" t="s">
+        <v>143</v>
+      </c>
+      <c r="E55" t="s">
+        <v>128</v>
+      </c>
+      <c r="F55">
+        <v>12</v>
+      </c>
+      <c r="G55" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>4</v>
+      </c>
+      <c r="B56">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" t="s">
+        <v>127</v>
+      </c>
+      <c r="E56" t="s">
+        <v>149</v>
+      </c>
+      <c r="F56">
+        <v>10</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>4</v>
+      </c>
+      <c r="B57">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>49</v>
+      </c>
+      <c r="D57" t="s">
+        <v>140</v>
+      </c>
+      <c r="E57" t="s">
+        <v>128</v>
+      </c>
+      <c r="F57">
+        <v>18</v>
+      </c>
+      <c r="G57" s="1">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="H57" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>4</v>
+      </c>
+      <c r="B58">
+        <v>12</v>
+      </c>
+      <c r="C58" t="s">
+        <v>91</v>
+      </c>
+      <c r="D58" t="s">
+        <v>223</v>
+      </c>
+      <c r="E58" t="s">
+        <v>47</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>4</v>
+      </c>
+      <c r="B59">
+        <v>13</v>
+      </c>
+      <c r="C59" t="s">
+        <v>228</v>
+      </c>
+      <c r="D59" t="s">
+        <v>156</v>
+      </c>
+      <c r="E59" t="s">
+        <v>128</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>4</v>
+      </c>
+      <c r="B60">
+        <v>14</v>
+      </c>
+      <c r="C60" t="s">
+        <v>225</v>
+      </c>
+      <c r="D60" t="s">
+        <v>156</v>
+      </c>
+      <c r="E60" t="s">
+        <v>47</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>4</v>
+      </c>
+      <c r="B61">
+        <v>15</v>
+      </c>
+      <c r="C61" t="s">
+        <v>93</v>
+      </c>
+      <c r="D61" t="s">
+        <v>157</v>
+      </c>
+      <c r="E61" t="s">
+        <v>128</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -7849,7 +10109,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B6E11CD-9E90-4D11-92A8-D8C539D81231}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="29.28515625" customWidth="1"/>
@@ -8931,6 +11191,357 @@
         <v>3</v>
       </c>
       <c r="G46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>4</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>55</v>
+      </c>
+      <c r="D47" t="s">
+        <v>223</v>
+      </c>
+      <c r="E47" t="s">
+        <v>128</v>
+      </c>
+      <c r="F47">
+        <v>7</v>
+      </c>
+      <c r="G47" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>4</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" t="s">
+        <v>212</v>
+      </c>
+      <c r="E48" t="s">
+        <v>128</v>
+      </c>
+      <c r="F48">
+        <v>6</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>4</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
+      </c>
+      <c r="C49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E49" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>4</v>
+      </c>
+      <c r="B50">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>229</v>
+      </c>
+      <c r="D50" t="s">
+        <v>215</v>
+      </c>
+      <c r="E50" t="s">
+        <v>128</v>
+      </c>
+      <c r="F50">
+        <v>11</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>4</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" t="s">
+        <v>223</v>
+      </c>
+      <c r="E51" t="s">
+        <v>128</v>
+      </c>
+      <c r="F51">
+        <v>8</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>4</v>
+      </c>
+      <c r="B52">
+        <v>6</v>
+      </c>
+      <c r="C52" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" t="s">
+        <v>156</v>
+      </c>
+      <c r="E52" t="s">
+        <v>128</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>4</v>
+      </c>
+      <c r="B53">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>96</v>
+      </c>
+      <c r="D53" t="s">
+        <v>143</v>
+      </c>
+      <c r="E53" t="s">
+        <v>128</v>
+      </c>
+      <c r="F53">
+        <v>10</v>
+      </c>
+      <c r="G53" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="H53" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>4</v>
+      </c>
+      <c r="B54">
+        <v>8</v>
+      </c>
+      <c r="C54" t="s">
+        <v>81</v>
+      </c>
+      <c r="D54" t="s">
+        <v>144</v>
+      </c>
+      <c r="E54" t="s">
+        <v>128</v>
+      </c>
+      <c r="F54">
+        <v>3</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>4</v>
+      </c>
+      <c r="B55">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>57</v>
+      </c>
+      <c r="D55" t="s">
+        <v>215</v>
+      </c>
+      <c r="E55" t="s">
+        <v>184</v>
+      </c>
+      <c r="F55">
+        <v>3</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>4</v>
+      </c>
+      <c r="B56">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" t="s">
+        <v>127</v>
+      </c>
+      <c r="E56" t="s">
+        <v>149</v>
+      </c>
+      <c r="F56">
+        <v>10</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>4</v>
+      </c>
+      <c r="B57">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>49</v>
+      </c>
+      <c r="D57" t="s">
+        <v>140</v>
+      </c>
+      <c r="E57" t="s">
+        <v>128</v>
+      </c>
+      <c r="F57">
+        <v>9</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>4</v>
+      </c>
+      <c r="B58">
+        <v>12</v>
+      </c>
+      <c r="C58" t="s">
+        <v>96</v>
+      </c>
+      <c r="D58" t="s">
+        <v>135</v>
+      </c>
+      <c r="E58" t="s">
+        <v>47</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>4</v>
+      </c>
+      <c r="B59">
+        <v>13</v>
+      </c>
+      <c r="C59" t="s">
+        <v>74</v>
+      </c>
+      <c r="D59" t="s">
+        <v>157</v>
+      </c>
+      <c r="E59" t="s">
+        <v>128</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>4</v>
+      </c>
+      <c r="B60">
+        <v>14</v>
+      </c>
+      <c r="C60" t="s">
+        <v>59</v>
+      </c>
+      <c r="D60" t="s">
+        <v>150</v>
+      </c>
+      <c r="E60" t="s">
+        <v>128</v>
+      </c>
+      <c r="F60">
+        <v>4</v>
+      </c>
+      <c r="G60" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>4</v>
+      </c>
+      <c r="B61">
+        <v>15</v>
+      </c>
+      <c r="C61" t="s">
+        <v>62</v>
+      </c>
+      <c r="D61" t="s">
+        <v>135</v>
+      </c>
+      <c r="E61" t="s">
+        <v>128</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61" s="1">
         <v>0</v>
       </c>
     </row>
@@ -8944,7 +11555,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222824F9-1AC4-4931-8973-86755A3F1C37}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -10024,6 +12635,357 @@
       </c>
       <c r="G46" s="1">
         <v>-0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>4</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47" t="s">
+        <v>212</v>
+      </c>
+      <c r="E47" t="s">
+        <v>128</v>
+      </c>
+      <c r="F47">
+        <v>14</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>4</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" t="s">
+        <v>212</v>
+      </c>
+      <c r="E48" t="s">
+        <v>128</v>
+      </c>
+      <c r="F48">
+        <v>6</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>4</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
+      </c>
+      <c r="C49" t="s">
+        <v>229</v>
+      </c>
+      <c r="D49" t="s">
+        <v>215</v>
+      </c>
+      <c r="E49" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49">
+        <v>11</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>4</v>
+      </c>
+      <c r="B50">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50" t="s">
+        <v>129</v>
+      </c>
+      <c r="E50" t="s">
+        <v>128</v>
+      </c>
+      <c r="F50">
+        <v>2</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>4</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>214</v>
+      </c>
+      <c r="D51" t="s">
+        <v>143</v>
+      </c>
+      <c r="E51" t="s">
+        <v>128</v>
+      </c>
+      <c r="F51">
+        <v>8</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>4</v>
+      </c>
+      <c r="B52">
+        <v>6</v>
+      </c>
+      <c r="C52" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" t="s">
+        <v>156</v>
+      </c>
+      <c r="E52" t="s">
+        <v>128</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>4</v>
+      </c>
+      <c r="B53">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" t="s">
+        <v>215</v>
+      </c>
+      <c r="E53" t="s">
+        <v>184</v>
+      </c>
+      <c r="F53">
+        <v>3</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>4</v>
+      </c>
+      <c r="B54">
+        <v>8</v>
+      </c>
+      <c r="C54" t="s">
+        <v>81</v>
+      </c>
+      <c r="D54" t="s">
+        <v>144</v>
+      </c>
+      <c r="E54" t="s">
+        <v>128</v>
+      </c>
+      <c r="F54">
+        <v>3</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>4</v>
+      </c>
+      <c r="B55">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>217</v>
+      </c>
+      <c r="D55" t="s">
+        <v>218</v>
+      </c>
+      <c r="E55" t="s">
+        <v>128</v>
+      </c>
+      <c r="F55">
+        <v>2</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="H55" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>4</v>
+      </c>
+      <c r="B56">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>51</v>
+      </c>
+      <c r="D56" t="s">
+        <v>143</v>
+      </c>
+      <c r="E56" t="s">
+        <v>128</v>
+      </c>
+      <c r="F56">
+        <v>24</v>
+      </c>
+      <c r="G56" s="1">
+        <v>1</v>
+      </c>
+      <c r="H56" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>4</v>
+      </c>
+      <c r="B57">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>49</v>
+      </c>
+      <c r="D57" t="s">
+        <v>140</v>
+      </c>
+      <c r="E57" t="s">
+        <v>128</v>
+      </c>
+      <c r="F57">
+        <v>9</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>4</v>
+      </c>
+      <c r="B58">
+        <v>12</v>
+      </c>
+      <c r="C58" t="s">
+        <v>96</v>
+      </c>
+      <c r="D58" t="s">
+        <v>135</v>
+      </c>
+      <c r="E58" t="s">
+        <v>47</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>4</v>
+      </c>
+      <c r="B59">
+        <v>13</v>
+      </c>
+      <c r="C59" t="s">
+        <v>59</v>
+      </c>
+      <c r="D59" t="s">
+        <v>150</v>
+      </c>
+      <c r="E59" t="s">
+        <v>128</v>
+      </c>
+      <c r="F59">
+        <v>4</v>
+      </c>
+      <c r="G59" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>4</v>
+      </c>
+      <c r="B60">
+        <v>14</v>
+      </c>
+      <c r="C60" t="s">
+        <v>191</v>
+      </c>
+      <c r="D60" t="s">
+        <v>150</v>
+      </c>
+      <c r="E60" t="s">
+        <v>230</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>4</v>
+      </c>
+      <c r="B61">
+        <v>15</v>
+      </c>
+      <c r="C61" t="s">
+        <v>189</v>
+      </c>
+      <c r="D61" t="s">
+        <v>138</v>
+      </c>
+      <c r="E61" t="s">
+        <v>128</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10036,10 +12998,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB542D51-1B6E-4A6F-B385-F419919DC470}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11118,6 +14080,357 @@
         <v>3</v>
       </c>
       <c r="G46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>4</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47" t="s">
+        <v>212</v>
+      </c>
+      <c r="E47" t="s">
+        <v>128</v>
+      </c>
+      <c r="F47">
+        <v>14</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>4</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>107</v>
+      </c>
+      <c r="D48" t="s">
+        <v>144</v>
+      </c>
+      <c r="E48" t="s">
+        <v>128</v>
+      </c>
+      <c r="F48">
+        <v>9</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>4</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
+      </c>
+      <c r="C49" t="s">
+        <v>104</v>
+      </c>
+      <c r="D49" t="s">
+        <v>140</v>
+      </c>
+      <c r="E49" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49">
+        <v>6</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>4</v>
+      </c>
+      <c r="B50">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>79</v>
+      </c>
+      <c r="D50" t="s">
+        <v>212</v>
+      </c>
+      <c r="E50" t="s">
+        <v>128</v>
+      </c>
+      <c r="F50">
+        <v>6</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>4</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s">
+        <v>44</v>
+      </c>
+      <c r="D51" t="s">
+        <v>156</v>
+      </c>
+      <c r="E51" t="s">
+        <v>128</v>
+      </c>
+      <c r="F51">
+        <v>2</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>4</v>
+      </c>
+      <c r="B52">
+        <v>6</v>
+      </c>
+      <c r="C52" t="s">
+        <v>81</v>
+      </c>
+      <c r="D52" t="s">
+        <v>144</v>
+      </c>
+      <c r="E52" t="s">
+        <v>128</v>
+      </c>
+      <c r="F52">
+        <v>3</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>4</v>
+      </c>
+      <c r="B53">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>147</v>
+      </c>
+      <c r="D53" t="s">
+        <v>140</v>
+      </c>
+      <c r="E53" t="s">
+        <v>128</v>
+      </c>
+      <c r="F53">
+        <v>5</v>
+      </c>
+      <c r="G53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>4</v>
+      </c>
+      <c r="B54">
+        <v>8</v>
+      </c>
+      <c r="C54" t="s">
+        <v>100</v>
+      </c>
+      <c r="D54" t="s">
+        <v>157</v>
+      </c>
+      <c r="E54" t="s">
+        <v>128</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>4</v>
+      </c>
+      <c r="B55">
+        <v>9</v>
+      </c>
+      <c r="C55" t="s">
+        <v>49</v>
+      </c>
+      <c r="D55" t="s">
+        <v>140</v>
+      </c>
+      <c r="E55" t="s">
+        <v>128</v>
+      </c>
+      <c r="F55">
+        <v>9</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>4</v>
+      </c>
+      <c r="B56">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>190</v>
+      </c>
+      <c r="D56" t="s">
+        <v>134</v>
+      </c>
+      <c r="E56" t="s">
+        <v>128</v>
+      </c>
+      <c r="F56">
+        <v>2</v>
+      </c>
+      <c r="G56" s="1">
+        <v>1</v>
+      </c>
+      <c r="H56" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>4</v>
+      </c>
+      <c r="B57">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>51</v>
+      </c>
+      <c r="D57" t="s">
+        <v>143</v>
+      </c>
+      <c r="E57" t="s">
+        <v>128</v>
+      </c>
+      <c r="F57">
+        <v>24</v>
+      </c>
+      <c r="G57" s="1">
+        <v>1</v>
+      </c>
+      <c r="H57" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>4</v>
+      </c>
+      <c r="B58">
+        <v>12</v>
+      </c>
+      <c r="C58" t="s">
+        <v>55</v>
+      </c>
+      <c r="D58" t="s">
+        <v>223</v>
+      </c>
+      <c r="E58" t="s">
+        <v>128</v>
+      </c>
+      <c r="F58">
+        <v>7</v>
+      </c>
+      <c r="G58" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>4</v>
+      </c>
+      <c r="B59">
+        <v>13</v>
+      </c>
+      <c r="C59" t="s">
+        <v>225</v>
+      </c>
+      <c r="D59" t="s">
+        <v>156</v>
+      </c>
+      <c r="E59" t="s">
+        <v>47</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>4</v>
+      </c>
+      <c r="B60">
+        <v>14</v>
+      </c>
+      <c r="C60" t="s">
+        <v>106</v>
+      </c>
+      <c r="D60" t="s">
+        <v>130</v>
+      </c>
+      <c r="E60" t="s">
+        <v>231</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>4</v>
+      </c>
+      <c r="B61">
+        <v>15</v>
+      </c>
+      <c r="C61" t="s">
+        <v>109</v>
+      </c>
+      <c r="D61" t="s">
+        <v>135</v>
+      </c>
+      <c r="E61" t="s">
+        <v>128</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+      <c r="G61" s="1">
         <v>0</v>
       </c>
     </row>

--- a/data/season_26_27.xlsx
+++ b/data/season_26_27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lukec\OneDrive\Documents\Rprojects\misc_projects\fpl_r\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D517CD-0862-4077-83BA-8A41C55E74B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7792A1-A47D-4BFD-805E-A340335ECF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="842" xr2:uid="{782628A8-4822-4E84-B9D1-9E9F8CA74FCB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="254">
   <si>
     <t>gameweek_id</t>
   </si>
@@ -731,6 +731,72 @@
   </si>
   <si>
     <t>Done (13)</t>
+  </si>
+  <si>
+    <t>Ødegaard</t>
+  </si>
+  <si>
+    <t>Kayode</t>
+  </si>
+  <si>
+    <t>Bogle</t>
+  </si>
+  <si>
+    <t>Delap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">João Pedro keyboard_arrow_down lens error </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mendy </t>
+  </si>
+  <si>
+    <t>Done (72) (P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">van Ewijk lens error </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shaw keyboard_arrow_up </t>
+  </si>
+  <si>
+    <t>Done (83) (P)</t>
+  </si>
+  <si>
+    <t>Done (21) (P)</t>
+  </si>
+  <si>
+    <t>Done (16) (P)</t>
+  </si>
+  <si>
+    <t>Done (11) (P)</t>
+  </si>
+  <si>
+    <t>Done (74) (P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Röhl lens error </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ødegaard </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayode keyboard_arrow_up </t>
+  </si>
+  <si>
+    <t>Done (68) (P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bogle </t>
+  </si>
+  <si>
+    <t>Done (84) (P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delap </t>
+  </si>
+  <si>
+    <t xml:space="preserve">João Pedro lens error </t>
   </si>
 </sst>
 </file>
@@ -738,7 +804,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -775,63 +841,17 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="13">
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0.0"/>
+      <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -938,10 +958,10 @@
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
+      <numFmt numFmtId="164" formatCode="#,##0.0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
@@ -960,16 +980,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}" name="Table1" displayName="Table1" ref="A1:J33" totalsRowShown="0">
-  <autoFilter ref="A1:J33" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}" name="Table1" displayName="Table1" ref="A1:J41" totalsRowShown="0">
+  <autoFilter ref="A1:J41" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{3DFDA157-BD05-4F91-BBC2-46C272CA2753}" name="date"/>
     <tableColumn id="2" xr3:uid="{E77E158C-7AE3-4435-9E81-D58EA8264AE1}" name="gameweek_id"/>
     <tableColumn id="3" xr3:uid="{4EC2B4AA-BB48-4F1C-AA23-865B4955D775}" name="season_standing"/>
     <tableColumn id="4" xr3:uid="{1A5CC8A7-E0BF-4423-9565-863589D0157E}" name="team"/>
-    <tableColumn id="5" xr3:uid="{7F46AE02-3FA0-4946-9C0E-9C4075370946}" name="season_transfers" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{CD26F816-00C7-4F1F-B5FB-E9B2D89B04C7}" name="overall_rank" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{4035F136-3D22-4E3D-951A-6F27496E67CD}" name="team_value" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{7F46AE02-3FA0-4946-9C0E-9C4075370946}" name="season_transfers" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{CD26F816-00C7-4F1F-B5FB-E9B2D89B04C7}" name="overall_rank" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{4035F136-3D22-4E3D-951A-6F27496E67CD}" name="team_value" dataDxfId="10"/>
     <tableColumn id="8" xr3:uid="{873B883E-CCA1-4415-9B58-AC7C5BD906B9}" name="gw_net"/>
     <tableColumn id="9" xr3:uid="{C348C7FD-EAB4-47B7-9C3E-0CF639A77318}" name="total"/>
     <tableColumn id="10" xr3:uid="{29219B07-DFC0-4696-B9A2-8E2F83EBFA88}" name="chip"/>
@@ -979,8 +999,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}" name="tim" displayName="tim" ref="A1:H61" totalsRowShown="0">
-  <autoFilter ref="A1:H61" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}" name="tim" displayName="tim" ref="A1:H76" totalsRowShown="0">
+  <autoFilter ref="A1:H76" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{67AFB369-C03A-462B-972F-AF60CDE2CFAB}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{44789776-FE7D-494A-B94B-2A601E85CB98}" name="player_slot"/>
@@ -996,8 +1016,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}" name="Table6" displayName="Table6" ref="A1:G19" totalsRowShown="0">
-  <autoFilter ref="A1:G19" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}" name="Table6" displayName="Table6" ref="A1:G23" totalsRowShown="0">
+  <autoFilter ref="A1:G23" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G2">
     <sortCondition ref="A1:A2"/>
   </sortState>
@@ -1015,16 +1035,16 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}" name="luke" displayName="luke" ref="A1:H61" totalsRowShown="0">
-  <autoFilter ref="A1:H61" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}" name="luke" displayName="luke" ref="A1:H76" totalsRowShown="0">
+  <autoFilter ref="A1:H76" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{E03C2832-F763-487D-BAF0-A846252C195D}" name="gameweek_id"/>
     <tableColumn id="7" xr3:uid="{442DEA06-1307-4EEB-981E-C530D39C1221}" name="player_slot"/>
     <tableColumn id="2" xr3:uid="{BE1D58D1-9C51-42D3-AA22-8CAB28CF8604}" name="player"/>
     <tableColumn id="3" xr3:uid="{BBA3FCC6-806B-41EB-9798-388AD565061B}" name="opposition"/>
     <tableColumn id="4" xr3:uid="{8A9B9F67-F40D-4762-ABF7-51D6948CCFB8}" name="status"/>
-    <tableColumn id="5" xr3:uid="{0F035BB3-B640-41E5-A9E0-B058E669931F}" name="points" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{0A20F07A-D2D6-40B3-BC30-00A5CB8DAF62}" name="importance" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{0F035BB3-B640-41E5-A9E0-B058E669931F}" name="points" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{0A20F07A-D2D6-40B3-BC30-00A5CB8DAF62}" name="importance" dataDxfId="8"/>
     <tableColumn id="8" xr3:uid="{D89A4728-D353-4540-BF9C-5C72EE4426C5}" name="captain"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1032,16 +1052,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}" name="james_c" displayName="james_c" ref="A1:H61" totalsRowShown="0">
-  <autoFilter ref="A1:H61" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}" name="james_c" displayName="james_c" ref="A1:H76" totalsRowShown="0">
+  <autoFilter ref="A1:H76" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{E3512878-F631-4A83-9CF0-34024519F60B}" name="gameweek_id"/>
     <tableColumn id="7" xr3:uid="{FB753C77-F849-4945-8ED7-323A572ADEC0}" name="player_slot"/>
     <tableColumn id="2" xr3:uid="{A4B086A9-1D65-498E-82B0-9E3DDE205578}" name="player"/>
     <tableColumn id="3" xr3:uid="{EAFCFA61-49CF-4629-92EB-1845A9C161E8}" name="opposition"/>
     <tableColumn id="4" xr3:uid="{49DB9FCA-5CA9-48A1-8F9F-B6D2EEAFF45A}" name="status"/>
-    <tableColumn id="5" xr3:uid="{7BB11C7C-223D-4CF7-877E-24F3DB42AEEB}" name="points" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{E23E9A84-2244-4003-A5C3-AE72E5161746}" name="importance" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{7BB11C7C-223D-4CF7-877E-24F3DB42AEEB}" name="points" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{E23E9A84-2244-4003-A5C3-AE72E5161746}" name="importance" dataDxfId="0"/>
     <tableColumn id="8" xr3:uid="{3D20344A-A9A9-43E1-96DD-6D5E7E4D95B7}" name="captain"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1049,16 +1069,16 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}" name="james_lm" displayName="james_lm" ref="A1:H61" totalsRowShown="0">
-  <autoFilter ref="A1:H61" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}" name="james_lm" displayName="james_lm" ref="A1:H76" totalsRowShown="0">
+  <autoFilter ref="A1:H76" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{85A61EA9-7D32-46E4-A518-261A47E355F4}" name="gameweek_id"/>
     <tableColumn id="7" xr3:uid="{86687FAE-12A2-4491-A6A8-B516A188A202}" name="player_slot"/>
     <tableColumn id="2" xr3:uid="{DDB067C6-F23D-40DD-9532-341379943214}" name="player"/>
     <tableColumn id="3" xr3:uid="{F61B9D23-0C8B-4F9C-9E09-DA9CF7A62D86}" name="opposition"/>
     <tableColumn id="4" xr3:uid="{F91D60CD-48C9-41AB-B219-B337A638004E}" name="status"/>
-    <tableColumn id="5" xr3:uid="{C9BD2123-E472-4AD8-B85E-08C7852BCADA}" name="points" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{D05930F1-9DF5-467C-8F3B-E6AAD4D53262}" name="importance" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{C9BD2123-E472-4AD8-B85E-08C7852BCADA}" name="points" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{D05930F1-9DF5-467C-8F3B-E6AAD4D53262}" name="importance" dataDxfId="6"/>
     <tableColumn id="8" xr3:uid="{2FE3DCC3-DA4C-4705-A219-64FBCE85BF11}" name="captain"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1066,8 +1086,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}" name="fred" displayName="fred" ref="A1:H61" totalsRowShown="0">
-  <autoFilter ref="A1:H61" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}" name="fred" displayName="fred" ref="A1:H76" totalsRowShown="0">
+  <autoFilter ref="A1:H76" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{BD2A7E80-7899-44F4-A0E0-E1951D803BBF}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{9A789C6B-DF65-4741-842B-32F8E097183F}" name="player_slot"/>
@@ -1083,8 +1103,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}" name="amy" displayName="amy" ref="A1:H61" totalsRowShown="0">
-  <autoFilter ref="A1:H61" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}" name="amy" displayName="amy" ref="A1:H76" totalsRowShown="0">
+  <autoFilter ref="A1:H76" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{3EEC9588-A154-4394-B1C6-FB872F361A10}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{CFDBEB1B-AC4B-4140-B9D5-FB0F16BBFA70}" name="player_slot"/>
@@ -1100,8 +1120,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}" name="andy" displayName="andy" ref="A1:H61" totalsRowShown="0">
-  <autoFilter ref="A1:H61" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}" name="andy" displayName="andy" ref="A1:H76" totalsRowShown="0">
+  <autoFilter ref="A1:H76" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{25B33829-3E10-4EA1-9ED1-D911F47A3168}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{4C06A930-A949-45AD-BF12-6F05B56443BE}" name="player_slot"/>
@@ -1117,8 +1137,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}" name="lewis" displayName="lewis" ref="A1:H61" totalsRowShown="0">
-  <autoFilter ref="A1:H61" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}" name="lewis" displayName="lewis" ref="A1:H76" totalsRowShown="0">
+  <autoFilter ref="A1:H76" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{14461CE9-1F87-4E76-B041-83CB47DED671}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{0AAB3767-3503-40AA-A974-A7C448E60023}" name="player_slot"/>
@@ -2439,9 +2459,241 @@
         <v>252</v>
       </c>
     </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <v>46283</v>
+      </c>
+      <c r="B34">
+        <v>5</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="2">
+        <v>2</v>
+      </c>
+      <c r="F34" s="2">
+        <v>368891</v>
+      </c>
+      <c r="G34" s="5">
+        <v>101.5</v>
+      </c>
+      <c r="H34">
+        <v>39</v>
+      </c>
+      <c r="I34">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>46283</v>
+      </c>
+      <c r="B35">
+        <v>5</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="2">
+        <v>4</v>
+      </c>
+      <c r="F35" s="2">
+        <v>1291540</v>
+      </c>
+      <c r="G35" s="5">
+        <v>100.3</v>
+      </c>
+      <c r="H35">
+        <v>58</v>
+      </c>
+      <c r="I35">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <v>46283</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+      <c r="C36">
+        <v>3</v>
+      </c>
+      <c r="D36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" s="2">
+        <v>3</v>
+      </c>
+      <c r="F36" s="2">
+        <v>2998268</v>
+      </c>
+      <c r="G36" s="5">
+        <v>99.9</v>
+      </c>
+      <c r="H36">
+        <v>52</v>
+      </c>
+      <c r="I36">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
+        <v>46283</v>
+      </c>
+      <c r="B37">
+        <v>5</v>
+      </c>
+      <c r="C37">
+        <v>4</v>
+      </c>
+      <c r="D37" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37" s="2">
+        <v>4</v>
+      </c>
+      <c r="F37" s="2">
+        <v>3107732</v>
+      </c>
+      <c r="G37" s="5">
+        <v>101.2</v>
+      </c>
+      <c r="H37">
+        <v>35</v>
+      </c>
+      <c r="I37">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
+        <v>46283</v>
+      </c>
+      <c r="B38">
+        <v>5</v>
+      </c>
+      <c r="C38">
+        <v>5</v>
+      </c>
+      <c r="D38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="2">
+        <v>3</v>
+      </c>
+      <c r="F38" s="2">
+        <v>3352154</v>
+      </c>
+      <c r="G38" s="5">
+        <v>99.8</v>
+      </c>
+      <c r="H38">
+        <v>31</v>
+      </c>
+      <c r="I38">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>46283</v>
+      </c>
+      <c r="B39">
+        <v>5</v>
+      </c>
+      <c r="C39">
+        <v>5</v>
+      </c>
+      <c r="D39" t="s">
+        <v>29</v>
+      </c>
+      <c r="E39" s="2">
+        <v>3</v>
+      </c>
+      <c r="F39" s="2">
+        <v>3352154</v>
+      </c>
+      <c r="G39" s="5">
+        <v>99.8</v>
+      </c>
+      <c r="H39">
+        <v>39</v>
+      </c>
+      <c r="I39">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <v>46283</v>
+      </c>
+      <c r="B40">
+        <v>5</v>
+      </c>
+      <c r="C40">
+        <v>7</v>
+      </c>
+      <c r="D40" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2">
+        <v>3416256</v>
+      </c>
+      <c r="G40" s="5">
+        <v>99.8</v>
+      </c>
+      <c r="H40">
+        <v>59</v>
+      </c>
+      <c r="I40">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>46283</v>
+      </c>
+      <c r="B41">
+        <v>5</v>
+      </c>
+      <c r="C41">
+        <v>8</v>
+      </c>
+      <c r="D41" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" s="2">
+        <v>3</v>
+      </c>
+      <c r="F41" s="2">
+        <v>4938024</v>
+      </c>
+      <c r="G41" s="5">
+        <v>101.7</v>
+      </c>
+      <c r="H41">
+        <v>42</v>
+      </c>
+      <c r="I41">
+        <v>295</v>
+      </c>
+    </row>
     <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <conditionalFormatting sqref="A2:J33">
+  <conditionalFormatting sqref="A2:J41">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>MOD($B2, 2) = 1</formula>
     </cfRule>
@@ -2458,7 +2710,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A820DAB-6033-4E1A-86E6-3C9D8203F219}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -3889,6 +4141,357 @@
       </c>
       <c r="G61" s="1">
         <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>5</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62" t="s">
+        <v>112</v>
+      </c>
+      <c r="E62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="H62" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>5</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>188</v>
+      </c>
+      <c r="D63" t="s">
+        <v>63</v>
+      </c>
+      <c r="E63" t="s">
+        <v>34</v>
+      </c>
+      <c r="F63">
+        <v>4</v>
+      </c>
+      <c r="G63" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>5</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>192</v>
+      </c>
+      <c r="D64" t="s">
+        <v>130</v>
+      </c>
+      <c r="E64" t="s">
+        <v>34</v>
+      </c>
+      <c r="F64">
+        <v>14</v>
+      </c>
+      <c r="G64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>5</v>
+      </c>
+      <c r="B65">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>35</v>
+      </c>
+      <c r="D65" t="s">
+        <v>112</v>
+      </c>
+      <c r="E65" t="s">
+        <v>34</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>5</v>
+      </c>
+      <c r="B66">
+        <v>5</v>
+      </c>
+      <c r="C66" t="s">
+        <v>250</v>
+      </c>
+      <c r="D66" t="s">
+        <v>83</v>
+      </c>
+      <c r="E66" t="s">
+        <v>76</v>
+      </c>
+      <c r="F66">
+        <v>5</v>
+      </c>
+      <c r="G66" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>5</v>
+      </c>
+      <c r="B67">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>70</v>
+      </c>
+      <c r="D67" t="s">
+        <v>112</v>
+      </c>
+      <c r="E67" t="s">
+        <v>238</v>
+      </c>
+      <c r="F67">
+        <v>2</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>5</v>
+      </c>
+      <c r="B68">
+        <v>7</v>
+      </c>
+      <c r="C68" t="s">
+        <v>173</v>
+      </c>
+      <c r="D68" t="s">
+        <v>63</v>
+      </c>
+      <c r="E68" t="s">
+        <v>251</v>
+      </c>
+      <c r="F68">
+        <v>8</v>
+      </c>
+      <c r="G68" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>5</v>
+      </c>
+      <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69" t="s">
+        <v>44</v>
+      </c>
+      <c r="D69" t="s">
+        <v>52</v>
+      </c>
+      <c r="E69" t="s">
+        <v>34</v>
+      </c>
+      <c r="F69">
+        <v>4</v>
+      </c>
+      <c r="G69" s="1">
+        <v>1.29</v>
+      </c>
+      <c r="H69" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>5</v>
+      </c>
+      <c r="B70">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
+        <v>96</v>
+      </c>
+      <c r="D70" t="s">
+        <v>56</v>
+      </c>
+      <c r="E70" t="s">
+        <v>34</v>
+      </c>
+      <c r="F70">
+        <v>2</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>5</v>
+      </c>
+      <c r="B71">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
+        <v>190</v>
+      </c>
+      <c r="D71" t="s">
+        <v>143</v>
+      </c>
+      <c r="E71" t="s">
+        <v>34</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>5</v>
+      </c>
+      <c r="B72">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>252</v>
+      </c>
+      <c r="D72" t="s">
+        <v>36</v>
+      </c>
+      <c r="E72" t="s">
+        <v>34</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>5</v>
+      </c>
+      <c r="B73">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>187</v>
+      </c>
+      <c r="D73" t="s">
+        <v>43</v>
+      </c>
+      <c r="E73" t="s">
+        <v>34</v>
+      </c>
+      <c r="F73">
+        <v>6</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>5</v>
+      </c>
+      <c r="B74">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
+        <v>253</v>
+      </c>
+      <c r="D74" t="s">
+        <v>56</v>
+      </c>
+      <c r="E74" t="s">
+        <v>47</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>5</v>
+      </c>
+      <c r="B75">
+        <v>14</v>
+      </c>
+      <c r="C75" t="s">
+        <v>84</v>
+      </c>
+      <c r="D75" t="s">
+        <v>157</v>
+      </c>
+      <c r="E75" t="s">
+        <v>34</v>
+      </c>
+      <c r="F75">
+        <v>14</v>
+      </c>
+      <c r="G75" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>5</v>
+      </c>
+      <c r="B76">
+        <v>15</v>
+      </c>
+      <c r="C76" t="s">
+        <v>189</v>
+      </c>
+      <c r="D76" t="s">
+        <v>43</v>
+      </c>
+      <c r="E76" t="s">
+        <v>34</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76" s="1">
+        <v>-0.14000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3910,7 +4513,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330229B3-0B25-4B18-9D20-120CB711B0FB}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -4302,6 +4905,86 @@
         <v>2</v>
       </c>
     </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>164</v>
+      </c>
+      <c r="C20" t="s">
+        <v>200</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="F20" t="s">
+        <v>166</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="F21" t="s">
+        <v>232</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" t="s">
+        <v>233</v>
+      </c>
+      <c r="D22">
+        <v>6</v>
+      </c>
+      <c r="F22" t="s">
+        <v>234</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>126</v>
+      </c>
+      <c r="C23" t="s">
+        <v>169</v>
+      </c>
+      <c r="D23">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>235</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -4312,7 +4995,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BFE37CD-4558-41F4-92EA-FE7453319710}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -5752,6 +6435,357 @@
         <v>0</v>
       </c>
     </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>5</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62" t="s">
+        <v>112</v>
+      </c>
+      <c r="E62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F62" s="3">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>5</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>35</v>
+      </c>
+      <c r="D63" t="s">
+        <v>112</v>
+      </c>
+      <c r="E63" t="s">
+        <v>34</v>
+      </c>
+      <c r="F63" s="3">
+        <v>1</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>5</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>219</v>
+      </c>
+      <c r="D64" t="s">
+        <v>143</v>
+      </c>
+      <c r="E64" t="s">
+        <v>34</v>
+      </c>
+      <c r="F64" s="3">
+        <v>4</v>
+      </c>
+      <c r="G64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>5</v>
+      </c>
+      <c r="B65">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>213</v>
+      </c>
+      <c r="D65" t="s">
+        <v>83</v>
+      </c>
+      <c r="E65" t="s">
+        <v>34</v>
+      </c>
+      <c r="F65" s="3">
+        <v>6</v>
+      </c>
+      <c r="G65" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>5</v>
+      </c>
+      <c r="B66">
+        <v>5</v>
+      </c>
+      <c r="C66" t="s">
+        <v>214</v>
+      </c>
+      <c r="D66" t="s">
+        <v>56</v>
+      </c>
+      <c r="E66" t="s">
+        <v>34</v>
+      </c>
+      <c r="F66" s="3">
+        <v>2</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>5</v>
+      </c>
+      <c r="B67">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>96</v>
+      </c>
+      <c r="D67" t="s">
+        <v>56</v>
+      </c>
+      <c r="E67" t="s">
+        <v>34</v>
+      </c>
+      <c r="F67" s="3">
+        <v>2</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>5</v>
+      </c>
+      <c r="B68">
+        <v>7</v>
+      </c>
+      <c r="C68" t="s">
+        <v>81</v>
+      </c>
+      <c r="D68" t="s">
+        <v>150</v>
+      </c>
+      <c r="E68" t="s">
+        <v>37</v>
+      </c>
+      <c r="F68" s="3">
+        <v>2</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>5</v>
+      </c>
+      <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69" t="s">
+        <v>152</v>
+      </c>
+      <c r="D69" t="s">
+        <v>36</v>
+      </c>
+      <c r="E69" t="s">
+        <v>34</v>
+      </c>
+      <c r="F69" s="3">
+        <v>2</v>
+      </c>
+      <c r="G69" s="1">
+        <v>1</v>
+      </c>
+      <c r="H69" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>5</v>
+      </c>
+      <c r="B70">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
+        <v>217</v>
+      </c>
+      <c r="D70" t="s">
+        <v>130</v>
+      </c>
+      <c r="E70" t="s">
+        <v>34</v>
+      </c>
+      <c r="F70" s="3">
+        <v>6</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>5</v>
+      </c>
+      <c r="B71">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
+        <v>49</v>
+      </c>
+      <c r="D71" t="s">
+        <v>63</v>
+      </c>
+      <c r="E71" t="s">
+        <v>34</v>
+      </c>
+      <c r="F71" s="3">
+        <v>12</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H71" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>5</v>
+      </c>
+      <c r="B72">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>236</v>
+      </c>
+      <c r="D72" t="s">
+        <v>56</v>
+      </c>
+      <c r="E72" t="s">
+        <v>47</v>
+      </c>
+      <c r="F72" s="3">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>5</v>
+      </c>
+      <c r="B73">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>216</v>
+      </c>
+      <c r="D73" t="s">
+        <v>46</v>
+      </c>
+      <c r="E73" t="s">
+        <v>47</v>
+      </c>
+      <c r="F73" s="3">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>5</v>
+      </c>
+      <c r="B74">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
+        <v>177</v>
+      </c>
+      <c r="D74" t="s">
+        <v>112</v>
+      </c>
+      <c r="E74" t="s">
+        <v>34</v>
+      </c>
+      <c r="F74" s="3">
+        <v>1</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>5</v>
+      </c>
+      <c r="B75">
+        <v>14</v>
+      </c>
+      <c r="C75" t="s">
+        <v>84</v>
+      </c>
+      <c r="D75" t="s">
+        <v>157</v>
+      </c>
+      <c r="E75" t="s">
+        <v>34</v>
+      </c>
+      <c r="F75" s="3">
+        <v>14</v>
+      </c>
+      <c r="G75" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>5</v>
+      </c>
+      <c r="B76">
+        <v>15</v>
+      </c>
+      <c r="C76" t="s">
+        <v>237</v>
+      </c>
+      <c r="D76" t="s">
+        <v>43</v>
+      </c>
+      <c r="E76" t="s">
+        <v>47</v>
+      </c>
+      <c r="F76" s="3">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5763,7 +6797,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A36F238-E413-4105-953D-9BEAF6AEF0DC}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
@@ -7199,6 +8233,357 @@
       </c>
       <c r="G61" s="1">
         <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>5</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>66</v>
+      </c>
+      <c r="D62" t="s">
+        <v>52</v>
+      </c>
+      <c r="E62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F62" s="3">
+        <v>4</v>
+      </c>
+      <c r="G62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>5</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>79</v>
+      </c>
+      <c r="D63" t="s">
+        <v>112</v>
+      </c>
+      <c r="E63" t="s">
+        <v>34</v>
+      </c>
+      <c r="F63" s="3">
+        <v>1</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>5</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>222</v>
+      </c>
+      <c r="D64" t="s">
+        <v>143</v>
+      </c>
+      <c r="E64" t="s">
+        <v>34</v>
+      </c>
+      <c r="F64" s="3">
+        <v>13</v>
+      </c>
+      <c r="G64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>5</v>
+      </c>
+      <c r="B65">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>69</v>
+      </c>
+      <c r="D65" t="s">
+        <v>33</v>
+      </c>
+      <c r="E65" t="s">
+        <v>34</v>
+      </c>
+      <c r="F65" s="3">
+        <v>6</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>5</v>
+      </c>
+      <c r="B66">
+        <v>5</v>
+      </c>
+      <c r="C66" t="s">
+        <v>70</v>
+      </c>
+      <c r="D66" t="s">
+        <v>112</v>
+      </c>
+      <c r="E66" t="s">
+        <v>238</v>
+      </c>
+      <c r="F66" s="3">
+        <v>2</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>5</v>
+      </c>
+      <c r="B67">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" t="s">
+        <v>52</v>
+      </c>
+      <c r="E67" t="s">
+        <v>34</v>
+      </c>
+      <c r="F67" s="3">
+        <v>2</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>5</v>
+      </c>
+      <c r="B68">
+        <v>7</v>
+      </c>
+      <c r="C68" t="s">
+        <v>214</v>
+      </c>
+      <c r="D68" t="s">
+        <v>56</v>
+      </c>
+      <c r="E68" t="s">
+        <v>34</v>
+      </c>
+      <c r="F68" s="3">
+        <v>2</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>5</v>
+      </c>
+      <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69" t="s">
+        <v>147</v>
+      </c>
+      <c r="D69" t="s">
+        <v>63</v>
+      </c>
+      <c r="E69" t="s">
+        <v>34</v>
+      </c>
+      <c r="F69" s="3">
+        <v>2</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>5</v>
+      </c>
+      <c r="B70">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
+        <v>236</v>
+      </c>
+      <c r="D70" t="s">
+        <v>56</v>
+      </c>
+      <c r="E70" t="s">
+        <v>47</v>
+      </c>
+      <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>5</v>
+      </c>
+      <c r="B71">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
+        <v>49</v>
+      </c>
+      <c r="D71" t="s">
+        <v>63</v>
+      </c>
+      <c r="E71" t="s">
+        <v>34</v>
+      </c>
+      <c r="F71" s="3">
+        <v>12</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H71" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>5</v>
+      </c>
+      <c r="B72">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>217</v>
+      </c>
+      <c r="D72" t="s">
+        <v>130</v>
+      </c>
+      <c r="E72" t="s">
+        <v>34</v>
+      </c>
+      <c r="F72" s="3">
+        <v>6</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>5</v>
+      </c>
+      <c r="B73">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>32</v>
+      </c>
+      <c r="D73" t="s">
+        <v>157</v>
+      </c>
+      <c r="E73" t="s">
+        <v>34</v>
+      </c>
+      <c r="F73" s="3">
+        <v>6</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>5</v>
+      </c>
+      <c r="B74">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
+        <v>239</v>
+      </c>
+      <c r="D74" t="s">
+        <v>54</v>
+      </c>
+      <c r="E74" t="s">
+        <v>47</v>
+      </c>
+      <c r="F74" s="3">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>5</v>
+      </c>
+      <c r="B75">
+        <v>14</v>
+      </c>
+      <c r="C75" t="s">
+        <v>240</v>
+      </c>
+      <c r="D75" t="s">
+        <v>52</v>
+      </c>
+      <c r="E75" t="s">
+        <v>241</v>
+      </c>
+      <c r="F75" s="3">
+        <v>2</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>5</v>
+      </c>
+      <c r="B76">
+        <v>15</v>
+      </c>
+      <c r="C76" t="s">
+        <v>59</v>
+      </c>
+      <c r="D76" t="s">
+        <v>171</v>
+      </c>
+      <c r="E76" t="s">
+        <v>242</v>
+      </c>
+      <c r="F76" s="3">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>-0.28999999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -7211,7 +8596,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0779779-8AAD-4A05-B64B-AAE55E86E147}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
@@ -8646,6 +10031,357 @@
         <v>0</v>
       </c>
       <c r="G61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>5</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>180</v>
+      </c>
+      <c r="D62" t="s">
+        <v>182</v>
+      </c>
+      <c r="E62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F62" s="3">
+        <v>3</v>
+      </c>
+      <c r="G62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>5</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>35</v>
+      </c>
+      <c r="D63" t="s">
+        <v>112</v>
+      </c>
+      <c r="E63" t="s">
+        <v>34</v>
+      </c>
+      <c r="F63" s="3">
+        <v>1</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>5</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>79</v>
+      </c>
+      <c r="D64" t="s">
+        <v>112</v>
+      </c>
+      <c r="E64" t="s">
+        <v>34</v>
+      </c>
+      <c r="F64" s="3">
+        <v>1</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>5</v>
+      </c>
+      <c r="B65">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>38</v>
+      </c>
+      <c r="D65" t="s">
+        <v>36</v>
+      </c>
+      <c r="E65" t="s">
+        <v>34</v>
+      </c>
+      <c r="F65" s="3">
+        <v>2</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="H65" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>5</v>
+      </c>
+      <c r="B66">
+        <v>5</v>
+      </c>
+      <c r="C66" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" t="s">
+        <v>52</v>
+      </c>
+      <c r="E66" t="s">
+        <v>34</v>
+      </c>
+      <c r="F66" s="3">
+        <v>2</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>5</v>
+      </c>
+      <c r="B67">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>80</v>
+      </c>
+      <c r="D67" t="s">
+        <v>63</v>
+      </c>
+      <c r="E67" t="s">
+        <v>34</v>
+      </c>
+      <c r="F67" s="3">
+        <v>17</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>5</v>
+      </c>
+      <c r="B68">
+        <v>7</v>
+      </c>
+      <c r="C68" t="s">
+        <v>81</v>
+      </c>
+      <c r="D68" t="s">
+        <v>150</v>
+      </c>
+      <c r="E68" t="s">
+        <v>37</v>
+      </c>
+      <c r="F68" s="3">
+        <v>2</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>5</v>
+      </c>
+      <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69" t="s">
+        <v>214</v>
+      </c>
+      <c r="D69" t="s">
+        <v>56</v>
+      </c>
+      <c r="E69" t="s">
+        <v>34</v>
+      </c>
+      <c r="F69" s="3">
+        <v>2</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>5</v>
+      </c>
+      <c r="B70">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
+        <v>84</v>
+      </c>
+      <c r="D70" t="s">
+        <v>157</v>
+      </c>
+      <c r="E70" t="s">
+        <v>34</v>
+      </c>
+      <c r="F70" s="3">
+        <v>14</v>
+      </c>
+      <c r="G70" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>5</v>
+      </c>
+      <c r="B71">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
+        <v>53</v>
+      </c>
+      <c r="D71" t="s">
+        <v>83</v>
+      </c>
+      <c r="E71" t="s">
+        <v>34</v>
+      </c>
+      <c r="F71" s="3">
+        <v>2</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>5</v>
+      </c>
+      <c r="B72">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>49</v>
+      </c>
+      <c r="D72" t="s">
+        <v>63</v>
+      </c>
+      <c r="E72" t="s">
+        <v>34</v>
+      </c>
+      <c r="F72" s="3">
+        <v>12</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H72" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>5</v>
+      </c>
+      <c r="B73">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>32</v>
+      </c>
+      <c r="D73" t="s">
+        <v>157</v>
+      </c>
+      <c r="E73" t="s">
+        <v>34</v>
+      </c>
+      <c r="F73" s="3">
+        <v>6</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>5</v>
+      </c>
+      <c r="B74">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
+        <v>87</v>
+      </c>
+      <c r="D74" t="s">
+        <v>54</v>
+      </c>
+      <c r="E74" t="s">
+        <v>34</v>
+      </c>
+      <c r="F74" s="3">
+        <v>9</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>5</v>
+      </c>
+      <c r="B75">
+        <v>14</v>
+      </c>
+      <c r="C75" t="s">
+        <v>226</v>
+      </c>
+      <c r="D75" t="s">
+        <v>54</v>
+      </c>
+      <c r="E75" t="s">
+        <v>243</v>
+      </c>
+      <c r="F75" s="3">
+        <v>1</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>5</v>
+      </c>
+      <c r="B76">
+        <v>15</v>
+      </c>
+      <c r="C76" t="s">
+        <v>85</v>
+      </c>
+      <c r="D76" t="s">
+        <v>178</v>
+      </c>
+      <c r="E76" t="s">
+        <v>244</v>
+      </c>
+      <c r="F76" s="3">
+        <v>1</v>
+      </c>
+      <c r="G76" s="1">
         <v>0</v>
       </c>
     </row>
@@ -8659,7 +10395,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{079AB974-BCF6-45DE-BAD2-52D6AC42558C}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -10099,6 +11835,357 @@
         <v>0</v>
       </c>
     </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>5</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62" t="s">
+        <v>112</v>
+      </c>
+      <c r="E62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>5</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>89</v>
+      </c>
+      <c r="D63" t="s">
+        <v>112</v>
+      </c>
+      <c r="E63" t="s">
+        <v>34</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>5</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>90</v>
+      </c>
+      <c r="D64" t="s">
+        <v>150</v>
+      </c>
+      <c r="E64" t="s">
+        <v>34</v>
+      </c>
+      <c r="F64">
+        <v>8</v>
+      </c>
+      <c r="G64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>5</v>
+      </c>
+      <c r="B65">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>94</v>
+      </c>
+      <c r="D65" t="s">
+        <v>171</v>
+      </c>
+      <c r="E65" t="s">
+        <v>34</v>
+      </c>
+      <c r="F65">
+        <v>7</v>
+      </c>
+      <c r="G65" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>5</v>
+      </c>
+      <c r="B66">
+        <v>5</v>
+      </c>
+      <c r="C66" t="s">
+        <v>40</v>
+      </c>
+      <c r="D66" t="s">
+        <v>52</v>
+      </c>
+      <c r="E66" t="s">
+        <v>34</v>
+      </c>
+      <c r="F66">
+        <v>2</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>5</v>
+      </c>
+      <c r="B67">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>82</v>
+      </c>
+      <c r="D67" t="s">
+        <v>63</v>
+      </c>
+      <c r="E67" t="s">
+        <v>245</v>
+      </c>
+      <c r="F67">
+        <v>5</v>
+      </c>
+      <c r="G67" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>5</v>
+      </c>
+      <c r="B68">
+        <v>7</v>
+      </c>
+      <c r="C68" t="s">
+        <v>70</v>
+      </c>
+      <c r="D68" t="s">
+        <v>112</v>
+      </c>
+      <c r="E68" t="s">
+        <v>238</v>
+      </c>
+      <c r="F68">
+        <v>2</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>5</v>
+      </c>
+      <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69" t="s">
+        <v>80</v>
+      </c>
+      <c r="D69" t="s">
+        <v>63</v>
+      </c>
+      <c r="E69" t="s">
+        <v>34</v>
+      </c>
+      <c r="F69">
+        <v>17</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>5</v>
+      </c>
+      <c r="B70">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
+        <v>236</v>
+      </c>
+      <c r="D70" t="s">
+        <v>56</v>
+      </c>
+      <c r="E70" t="s">
+        <v>47</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>5</v>
+      </c>
+      <c r="B71">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
+        <v>53</v>
+      </c>
+      <c r="D71" t="s">
+        <v>83</v>
+      </c>
+      <c r="E71" t="s">
+        <v>34</v>
+      </c>
+      <c r="F71">
+        <v>2</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>5</v>
+      </c>
+      <c r="B72">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>49</v>
+      </c>
+      <c r="D72" t="s">
+        <v>63</v>
+      </c>
+      <c r="E72" t="s">
+        <v>34</v>
+      </c>
+      <c r="F72">
+        <v>12</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H72" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>5</v>
+      </c>
+      <c r="B73">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>91</v>
+      </c>
+      <c r="D73" t="s">
+        <v>33</v>
+      </c>
+      <c r="E73" t="s">
+        <v>47</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>5</v>
+      </c>
+      <c r="B74">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
+        <v>246</v>
+      </c>
+      <c r="D74" t="s">
+        <v>130</v>
+      </c>
+      <c r="E74" t="s">
+        <v>47</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>5</v>
+      </c>
+      <c r="B75">
+        <v>14</v>
+      </c>
+      <c r="C75" t="s">
+        <v>240</v>
+      </c>
+      <c r="D75" t="s">
+        <v>52</v>
+      </c>
+      <c r="E75" t="s">
+        <v>241</v>
+      </c>
+      <c r="F75">
+        <v>2</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>5</v>
+      </c>
+      <c r="B76">
+        <v>15</v>
+      </c>
+      <c r="C76" t="s">
+        <v>93</v>
+      </c>
+      <c r="D76" t="s">
+        <v>178</v>
+      </c>
+      <c r="E76" t="s">
+        <v>34</v>
+      </c>
+      <c r="F76">
+        <v>2</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -10109,7 +12196,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B6E11CD-9E90-4D11-92A8-D8C539D81231}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="29.28515625" customWidth="1"/>
@@ -11542,6 +13629,357 @@
         <v>1</v>
       </c>
       <c r="G61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>5</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>55</v>
+      </c>
+      <c r="D62" t="s">
+        <v>33</v>
+      </c>
+      <c r="E62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F62">
+        <v>2</v>
+      </c>
+      <c r="G62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>5</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>35</v>
+      </c>
+      <c r="D63" t="s">
+        <v>112</v>
+      </c>
+      <c r="E63" t="s">
+        <v>34</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>5</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>40</v>
+      </c>
+      <c r="D64" t="s">
+        <v>52</v>
+      </c>
+      <c r="E64" t="s">
+        <v>34</v>
+      </c>
+      <c r="F64">
+        <v>2</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>5</v>
+      </c>
+      <c r="B65">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>69</v>
+      </c>
+      <c r="D65" t="s">
+        <v>33</v>
+      </c>
+      <c r="E65" t="s">
+        <v>34</v>
+      </c>
+      <c r="F65">
+        <v>6</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>5</v>
+      </c>
+      <c r="B66">
+        <v>5</v>
+      </c>
+      <c r="C66" t="s">
+        <v>59</v>
+      </c>
+      <c r="D66" t="s">
+        <v>171</v>
+      </c>
+      <c r="E66" t="s">
+        <v>242</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>5</v>
+      </c>
+      <c r="B67">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" t="s">
+        <v>52</v>
+      </c>
+      <c r="E67" t="s">
+        <v>34</v>
+      </c>
+      <c r="F67">
+        <v>2</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>5</v>
+      </c>
+      <c r="B68">
+        <v>7</v>
+      </c>
+      <c r="C68" t="s">
+        <v>96</v>
+      </c>
+      <c r="D68" t="s">
+        <v>56</v>
+      </c>
+      <c r="E68" t="s">
+        <v>34</v>
+      </c>
+      <c r="F68">
+        <v>2</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="H68" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>5</v>
+      </c>
+      <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69" t="s">
+        <v>81</v>
+      </c>
+      <c r="D69" t="s">
+        <v>150</v>
+      </c>
+      <c r="E69" t="s">
+        <v>37</v>
+      </c>
+      <c r="F69">
+        <v>2</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>5</v>
+      </c>
+      <c r="B70">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
+        <v>57</v>
+      </c>
+      <c r="D70" t="s">
+        <v>157</v>
+      </c>
+      <c r="E70" t="s">
+        <v>58</v>
+      </c>
+      <c r="F70">
+        <v>8</v>
+      </c>
+      <c r="G70" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>5</v>
+      </c>
+      <c r="B71">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
+        <v>53</v>
+      </c>
+      <c r="D71" t="s">
+        <v>83</v>
+      </c>
+      <c r="E71" t="s">
+        <v>34</v>
+      </c>
+      <c r="F71">
+        <v>2</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>5</v>
+      </c>
+      <c r="B72">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>49</v>
+      </c>
+      <c r="D72" t="s">
+        <v>63</v>
+      </c>
+      <c r="E72" t="s">
+        <v>34</v>
+      </c>
+      <c r="F72">
+        <v>12</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H72" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>5</v>
+      </c>
+      <c r="B73">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>96</v>
+      </c>
+      <c r="D73" t="s">
+        <v>46</v>
+      </c>
+      <c r="E73" t="s">
+        <v>47</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>5</v>
+      </c>
+      <c r="B74">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
+        <v>229</v>
+      </c>
+      <c r="D74" t="s">
+        <v>157</v>
+      </c>
+      <c r="E74" t="s">
+        <v>34</v>
+      </c>
+      <c r="F74">
+        <v>6</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>5</v>
+      </c>
+      <c r="B75">
+        <v>14</v>
+      </c>
+      <c r="C75" t="s">
+        <v>74</v>
+      </c>
+      <c r="D75" t="s">
+        <v>178</v>
+      </c>
+      <c r="E75" t="s">
+        <v>34</v>
+      </c>
+      <c r="F75">
+        <v>17</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>5</v>
+      </c>
+      <c r="B76">
+        <v>15</v>
+      </c>
+      <c r="C76" t="s">
+        <v>62</v>
+      </c>
+      <c r="D76" t="s">
+        <v>46</v>
+      </c>
+      <c r="E76" t="s">
+        <v>34</v>
+      </c>
+      <c r="F76">
+        <v>2</v>
+      </c>
+      <c r="G76" s="1">
         <v>0</v>
       </c>
     </row>
@@ -11555,7 +13993,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222824F9-1AC4-4931-8973-86755A3F1C37}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -12985,6 +15423,357 @@
         <v>1</v>
       </c>
       <c r="G61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>5</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62" t="s">
+        <v>112</v>
+      </c>
+      <c r="E62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>5</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>35</v>
+      </c>
+      <c r="D63" t="s">
+        <v>112</v>
+      </c>
+      <c r="E63" t="s">
+        <v>34</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>5</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>189</v>
+      </c>
+      <c r="D64" t="s">
+        <v>43</v>
+      </c>
+      <c r="E64" t="s">
+        <v>34</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>5</v>
+      </c>
+      <c r="B65">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>38</v>
+      </c>
+      <c r="D65" t="s">
+        <v>36</v>
+      </c>
+      <c r="E65" t="s">
+        <v>34</v>
+      </c>
+      <c r="F65">
+        <v>2</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>5</v>
+      </c>
+      <c r="B66">
+        <v>5</v>
+      </c>
+      <c r="C66" t="s">
+        <v>214</v>
+      </c>
+      <c r="D66" t="s">
+        <v>56</v>
+      </c>
+      <c r="E66" t="s">
+        <v>34</v>
+      </c>
+      <c r="F66">
+        <v>2</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>5</v>
+      </c>
+      <c r="B67">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" t="s">
+        <v>52</v>
+      </c>
+      <c r="E67" t="s">
+        <v>34</v>
+      </c>
+      <c r="F67">
+        <v>2</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>5</v>
+      </c>
+      <c r="B68">
+        <v>7</v>
+      </c>
+      <c r="C68" t="s">
+        <v>59</v>
+      </c>
+      <c r="D68" t="s">
+        <v>171</v>
+      </c>
+      <c r="E68" t="s">
+        <v>242</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>5</v>
+      </c>
+      <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69" t="s">
+        <v>247</v>
+      </c>
+      <c r="D69" t="s">
+        <v>112</v>
+      </c>
+      <c r="E69" t="s">
+        <v>238</v>
+      </c>
+      <c r="F69">
+        <v>2</v>
+      </c>
+      <c r="G69" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>5</v>
+      </c>
+      <c r="B70">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
+        <v>217</v>
+      </c>
+      <c r="D70" t="s">
+        <v>130</v>
+      </c>
+      <c r="E70" t="s">
+        <v>34</v>
+      </c>
+      <c r="F70">
+        <v>12</v>
+      </c>
+      <c r="G70" s="1">
+        <v>1.71</v>
+      </c>
+      <c r="H70" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>5</v>
+      </c>
+      <c r="B71">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
+        <v>236</v>
+      </c>
+      <c r="D71" t="s">
+        <v>56</v>
+      </c>
+      <c r="E71" t="s">
+        <v>47</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0</v>
+      </c>
+      <c r="H71" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>5</v>
+      </c>
+      <c r="B72">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>49</v>
+      </c>
+      <c r="D72" t="s">
+        <v>63</v>
+      </c>
+      <c r="E72" t="s">
+        <v>34</v>
+      </c>
+      <c r="F72">
+        <v>6</v>
+      </c>
+      <c r="G72" s="1">
+        <v>-0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>5</v>
+      </c>
+      <c r="B73">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>96</v>
+      </c>
+      <c r="D73" t="s">
+        <v>46</v>
+      </c>
+      <c r="E73" t="s">
+        <v>47</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>5</v>
+      </c>
+      <c r="B74">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
+        <v>248</v>
+      </c>
+      <c r="D74" t="s">
+        <v>171</v>
+      </c>
+      <c r="E74" t="s">
+        <v>249</v>
+      </c>
+      <c r="F74">
+        <v>6</v>
+      </c>
+      <c r="G74" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>5</v>
+      </c>
+      <c r="B75">
+        <v>14</v>
+      </c>
+      <c r="C75" t="s">
+        <v>57</v>
+      </c>
+      <c r="D75" t="s">
+        <v>157</v>
+      </c>
+      <c r="E75" t="s">
+        <v>58</v>
+      </c>
+      <c r="F75">
+        <v>8</v>
+      </c>
+      <c r="G75" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>5</v>
+      </c>
+      <c r="B76">
+        <v>15</v>
+      </c>
+      <c r="C76" t="s">
+        <v>229</v>
+      </c>
+      <c r="D76" t="s">
+        <v>157</v>
+      </c>
+      <c r="E76" t="s">
+        <v>34</v>
+      </c>
+      <c r="F76">
+        <v>6</v>
+      </c>
+      <c r="G76" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12998,7 +15787,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB542D51-1B6E-4A6F-B385-F419919DC470}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -14431,6 +17220,357 @@
         <v>1</v>
       </c>
       <c r="G61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>5</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62" t="s">
+        <v>112</v>
+      </c>
+      <c r="E62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>5</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>107</v>
+      </c>
+      <c r="D63" t="s">
+        <v>150</v>
+      </c>
+      <c r="E63" t="s">
+        <v>34</v>
+      </c>
+      <c r="F63">
+        <v>6</v>
+      </c>
+      <c r="G63" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>5</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>104</v>
+      </c>
+      <c r="D64" t="s">
+        <v>63</v>
+      </c>
+      <c r="E64" t="s">
+        <v>34</v>
+      </c>
+      <c r="F64">
+        <v>4</v>
+      </c>
+      <c r="G64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>5</v>
+      </c>
+      <c r="B65">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>79</v>
+      </c>
+      <c r="D65" t="s">
+        <v>112</v>
+      </c>
+      <c r="E65" t="s">
+        <v>34</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>5</v>
+      </c>
+      <c r="B66">
+        <v>5</v>
+      </c>
+      <c r="C66" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" t="s">
+        <v>52</v>
+      </c>
+      <c r="E66" t="s">
+        <v>34</v>
+      </c>
+      <c r="F66">
+        <v>2</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>5</v>
+      </c>
+      <c r="B67">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>81</v>
+      </c>
+      <c r="D67" t="s">
+        <v>150</v>
+      </c>
+      <c r="E67" t="s">
+        <v>37</v>
+      </c>
+      <c r="F67">
+        <v>2</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>5</v>
+      </c>
+      <c r="B68">
+        <v>7</v>
+      </c>
+      <c r="C68" t="s">
+        <v>147</v>
+      </c>
+      <c r="D68" t="s">
+        <v>63</v>
+      </c>
+      <c r="E68" t="s">
+        <v>34</v>
+      </c>
+      <c r="F68">
+        <v>2</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>5</v>
+      </c>
+      <c r="B69">
+        <v>8</v>
+      </c>
+      <c r="C69" t="s">
+        <v>100</v>
+      </c>
+      <c r="D69" t="s">
+        <v>178</v>
+      </c>
+      <c r="E69" t="s">
+        <v>34</v>
+      </c>
+      <c r="F69">
+        <v>5</v>
+      </c>
+      <c r="G69" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>5</v>
+      </c>
+      <c r="B70">
+        <v>9</v>
+      </c>
+      <c r="C70" t="s">
+        <v>49</v>
+      </c>
+      <c r="D70" t="s">
+        <v>63</v>
+      </c>
+      <c r="E70" t="s">
+        <v>34</v>
+      </c>
+      <c r="F70">
+        <v>6</v>
+      </c>
+      <c r="G70" s="1">
+        <v>-0.56999999999999995</v>
+      </c>
+      <c r="H70" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>5</v>
+      </c>
+      <c r="B71">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
+        <v>190</v>
+      </c>
+      <c r="D71" t="s">
+        <v>143</v>
+      </c>
+      <c r="E71" t="s">
+        <v>34</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>1.86</v>
+      </c>
+      <c r="H71" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>5</v>
+      </c>
+      <c r="B72">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>236</v>
+      </c>
+      <c r="D72" t="s">
+        <v>56</v>
+      </c>
+      <c r="E72" t="s">
+        <v>47</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>5</v>
+      </c>
+      <c r="B73">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>55</v>
+      </c>
+      <c r="D73" t="s">
+        <v>33</v>
+      </c>
+      <c r="E73" t="s">
+        <v>34</v>
+      </c>
+      <c r="F73">
+        <v>2</v>
+      </c>
+      <c r="G73" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>5</v>
+      </c>
+      <c r="B74">
+        <v>13</v>
+      </c>
+      <c r="C74" t="s">
+        <v>240</v>
+      </c>
+      <c r="D74" t="s">
+        <v>52</v>
+      </c>
+      <c r="E74" t="s">
+        <v>241</v>
+      </c>
+      <c r="F74">
+        <v>2</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>5</v>
+      </c>
+      <c r="B75">
+        <v>14</v>
+      </c>
+      <c r="C75" t="s">
+        <v>106</v>
+      </c>
+      <c r="D75" t="s">
+        <v>134</v>
+      </c>
+      <c r="E75" t="s">
+        <v>47</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>5</v>
+      </c>
+      <c r="B76">
+        <v>15</v>
+      </c>
+      <c r="C76" t="s">
+        <v>109</v>
+      </c>
+      <c r="D76" t="s">
+        <v>46</v>
+      </c>
+      <c r="E76" t="s">
+        <v>34</v>
+      </c>
+      <c r="F76">
+        <v>4</v>
+      </c>
+      <c r="G76" s="1">
         <v>0</v>
       </c>
     </row>

--- a/data/season_26_27.xlsx
+++ b/data/season_26_27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lukec\OneDrive\Documents\Rprojects\misc_projects\fpl_r\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7792A1-A47D-4BFD-805E-A340335ECF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3973A817-3001-434B-94F1-EFFBD340E31C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="842" xr2:uid="{782628A8-4822-4E84-B9D1-9E9F8CA74FCB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="285">
   <si>
     <t>gameweek_id</t>
   </si>
@@ -797,6 +797,99 @@
   </si>
   <si>
     <t xml:space="preserve">João Pedro lens error </t>
+  </si>
+  <si>
+    <t>Groß</t>
+  </si>
+  <si>
+    <t>Hume</t>
+  </si>
+  <si>
+    <t>Affengruber</t>
+  </si>
+  <si>
+    <t>Belloumi</t>
+  </si>
+  <si>
+    <t>Kostoulas</t>
+  </si>
+  <si>
+    <t>Anderson</t>
+  </si>
+  <si>
+    <t>Röhl</t>
+  </si>
+  <si>
+    <t>Yalcouyé</t>
+  </si>
+  <si>
+    <t>King</t>
+  </si>
+  <si>
+    <t>fred</t>
+  </si>
+  <si>
+    <t>Saka</t>
+  </si>
+  <si>
+    <t>Done (87)</t>
+  </si>
+  <si>
+    <t>Done (79)</t>
+  </si>
+  <si>
+    <t>Done (71)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szoboszlai lens error </t>
+  </si>
+  <si>
+    <t>Done (38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Affengruber </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calvert-Lewin keyboard_arrow_up </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szoboszlai keyboard_arrow_down lens error </t>
+  </si>
+  <si>
+    <t>Done (12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">King </t>
+  </si>
+  <si>
+    <t>Done (75)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yalcouyé </t>
+  </si>
+  <si>
+    <t>Done (22)</t>
+  </si>
+  <si>
+    <t>Done (67)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belloumi keyboard_arrow_up </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kostoulas </t>
+  </si>
+  <si>
+    <t>Done (59)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacquet keyboard_arrow_up </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saka </t>
+  </si>
+  <si>
+    <t>Done (24)</t>
   </si>
 </sst>
 </file>
@@ -846,12 +939,52 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="15">
     <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -958,6 +1091,12 @@
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="164" formatCode="#,##0.0"/>
     </dxf>
     <dxf>
@@ -980,16 +1119,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}" name="Table1" displayName="Table1" ref="A1:J41" totalsRowShown="0">
-  <autoFilter ref="A1:J41" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}" name="Table1" displayName="Table1" ref="A1:J49" totalsRowShown="0">
+  <autoFilter ref="A1:J49" xr:uid="{78833D36-2EA2-4E98-A4BE-9C07E0FF338B}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{3DFDA157-BD05-4F91-BBC2-46C272CA2753}" name="date"/>
     <tableColumn id="2" xr3:uid="{E77E158C-7AE3-4435-9E81-D58EA8264AE1}" name="gameweek_id"/>
     <tableColumn id="3" xr3:uid="{4EC2B4AA-BB48-4F1C-AA23-865B4955D775}" name="season_standing"/>
     <tableColumn id="4" xr3:uid="{1A5CC8A7-E0BF-4423-9565-863589D0157E}" name="team"/>
-    <tableColumn id="5" xr3:uid="{7F46AE02-3FA0-4946-9C0E-9C4075370946}" name="season_transfers" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{CD26F816-00C7-4F1F-B5FB-E9B2D89B04C7}" name="overall_rank" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{4035F136-3D22-4E3D-951A-6F27496E67CD}" name="team_value" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{7F46AE02-3FA0-4946-9C0E-9C4075370946}" name="season_transfers" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{CD26F816-00C7-4F1F-B5FB-E9B2D89B04C7}" name="overall_rank" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{4035F136-3D22-4E3D-951A-6F27496E67CD}" name="team_value" dataDxfId="12"/>
     <tableColumn id="8" xr3:uid="{873B883E-CCA1-4415-9B58-AC7C5BD906B9}" name="gw_net"/>
     <tableColumn id="9" xr3:uid="{C348C7FD-EAB4-47B7-9C3E-0CF639A77318}" name="total"/>
     <tableColumn id="10" xr3:uid="{29219B07-DFC0-4696-B9A2-8E2F83EBFA88}" name="chip"/>
@@ -999,8 +1138,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}" name="tim" displayName="tim" ref="A1:H76" totalsRowShown="0">
-  <autoFilter ref="A1:H76" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}" name="tim" displayName="tim" ref="A1:H91" totalsRowShown="0">
+  <autoFilter ref="A1:H91" xr:uid="{26A6712A-76F7-43F4-AFCD-FC4B34C739CB}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{67AFB369-C03A-462B-972F-AF60CDE2CFAB}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{44789776-FE7D-494A-B94B-2A601E85CB98}" name="player_slot"/>
@@ -1016,8 +1155,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}" name="Table6" displayName="Table6" ref="A1:G23" totalsRowShown="0">
-  <autoFilter ref="A1:G23" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}" name="Table6" displayName="Table6" ref="A1:G33" totalsRowShown="0">
+  <autoFilter ref="A1:G33" xr:uid="{834A82F0-C4CB-4F10-8445-E17334191908}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G2">
     <sortCondition ref="A1:A2"/>
   </sortState>
@@ -1035,16 +1174,16 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}" name="luke" displayName="luke" ref="A1:H76" totalsRowShown="0">
-  <autoFilter ref="A1:H76" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}" name="luke" displayName="luke" ref="A1:H91" totalsRowShown="0">
+  <autoFilter ref="A1:H91" xr:uid="{0C79F2B5-2DA2-4DDC-B141-6C178423EFC9}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{E03C2832-F763-487D-BAF0-A846252C195D}" name="gameweek_id"/>
     <tableColumn id="7" xr3:uid="{442DEA06-1307-4EEB-981E-C530D39C1221}" name="player_slot"/>
     <tableColumn id="2" xr3:uid="{BE1D58D1-9C51-42D3-AA22-8CAB28CF8604}" name="player"/>
     <tableColumn id="3" xr3:uid="{BBA3FCC6-806B-41EB-9798-388AD565061B}" name="opposition"/>
     <tableColumn id="4" xr3:uid="{8A9B9F67-F40D-4762-ABF7-51D6948CCFB8}" name="status"/>
-    <tableColumn id="5" xr3:uid="{0F035BB3-B640-41E5-A9E0-B058E669931F}" name="points" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{0A20F07A-D2D6-40B3-BC30-00A5CB8DAF62}" name="importance" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{0F035BB3-B640-41E5-A9E0-B058E669931F}" name="points" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{0A20F07A-D2D6-40B3-BC30-00A5CB8DAF62}" name="importance" dataDxfId="10"/>
     <tableColumn id="8" xr3:uid="{D89A4728-D353-4540-BF9C-5C72EE4426C5}" name="captain"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1052,16 +1191,16 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}" name="james_c" displayName="james_c" ref="A1:H76" totalsRowShown="0">
-  <autoFilter ref="A1:H76" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}" name="james_c" displayName="james_c" ref="A1:H91" totalsRowShown="0">
+  <autoFilter ref="A1:H91" xr:uid="{40743D84-5D1D-4F09-968D-FD072472C000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{E3512878-F631-4A83-9CF0-34024519F60B}" name="gameweek_id"/>
     <tableColumn id="7" xr3:uid="{FB753C77-F849-4945-8ED7-323A572ADEC0}" name="player_slot"/>
     <tableColumn id="2" xr3:uid="{A4B086A9-1D65-498E-82B0-9E3DDE205578}" name="player"/>
     <tableColumn id="3" xr3:uid="{EAFCFA61-49CF-4629-92EB-1845A9C161E8}" name="opposition"/>
     <tableColumn id="4" xr3:uid="{49DB9FCA-5CA9-48A1-8F9F-B6D2EEAFF45A}" name="status"/>
-    <tableColumn id="5" xr3:uid="{7BB11C7C-223D-4CF7-877E-24F3DB42AEEB}" name="points" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{E23E9A84-2244-4003-A5C3-AE72E5161746}" name="importance" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{7BB11C7C-223D-4CF7-877E-24F3DB42AEEB}" name="points" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{E23E9A84-2244-4003-A5C3-AE72E5161746}" name="importance" dataDxfId="8"/>
     <tableColumn id="8" xr3:uid="{3D20344A-A9A9-43E1-96DD-6D5E7E4D95B7}" name="captain"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1069,8 +1208,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}" name="james_lm" displayName="james_lm" ref="A1:H76" totalsRowShown="0">
-  <autoFilter ref="A1:H76" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}" name="james_lm" displayName="james_lm" ref="A1:H91" totalsRowShown="0">
+  <autoFilter ref="A1:H91" xr:uid="{C4F18A3A-3962-4DE6-B26A-1593D6AA9FEE}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{85A61EA9-7D32-46E4-A518-261A47E355F4}" name="gameweek_id"/>
     <tableColumn id="7" xr3:uid="{86687FAE-12A2-4491-A6A8-B516A188A202}" name="player_slot"/>
@@ -1086,8 +1225,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}" name="fred" displayName="fred" ref="A1:H76" totalsRowShown="0">
-  <autoFilter ref="A1:H76" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}" name="fred" displayName="fred" ref="A1:H91" totalsRowShown="0">
+  <autoFilter ref="A1:H91" xr:uid="{33108629-B823-45B7-88A6-BF79B59C7288}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{BD2A7E80-7899-44F4-A0E0-E1951D803BBF}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{9A789C6B-DF65-4741-842B-32F8E097183F}" name="player_slot"/>
@@ -1103,8 +1242,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}" name="amy" displayName="amy" ref="A1:H76" totalsRowShown="0">
-  <autoFilter ref="A1:H76" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}" name="amy" displayName="amy" ref="A1:H91" totalsRowShown="0">
+  <autoFilter ref="A1:H91" xr:uid="{2F672808-FFBF-4133-820A-C671D4E6F70B}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{3EEC9588-A154-4394-B1C6-FB872F361A10}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{CFDBEB1B-AC4B-4140-B9D5-FB0F16BBFA70}" name="player_slot"/>
@@ -1120,8 +1259,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}" name="andy" displayName="andy" ref="A1:H76" totalsRowShown="0">
-  <autoFilter ref="A1:H76" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}" name="andy" displayName="andy" ref="A1:H91" totalsRowShown="0">
+  <autoFilter ref="A1:H91" xr:uid="{332D2B49-9F65-4531-A0B2-0CB5ED32ABEB}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{25B33829-3E10-4EA1-9ED1-D911F47A3168}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{4C06A930-A949-45AD-BF12-6F05B56443BE}" name="player_slot"/>
@@ -1137,8 +1276,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}" name="lewis" displayName="lewis" ref="A1:H76" totalsRowShown="0">
-  <autoFilter ref="A1:H76" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}" name="lewis" displayName="lewis" ref="A1:H91" totalsRowShown="0">
+  <autoFilter ref="A1:H91" xr:uid="{E068B727-5A63-4591-897A-314D6529CF8E}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{14461CE9-1F87-4E76-B041-83CB47DED671}" name="gameweek_id"/>
     <tableColumn id="2" xr3:uid="{0AAB3767-3503-40AA-A974-A7C448E60023}" name="player_slot"/>
@@ -2691,13 +2830,245 @@
         <v>295</v>
       </c>
     </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
+        <v>46305</v>
+      </c>
+      <c r="B42">
+        <v>6</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" s="2">
+        <v>2</v>
+      </c>
+      <c r="F42" s="2">
+        <v>205556</v>
+      </c>
+      <c r="G42" s="5">
+        <v>102</v>
+      </c>
+      <c r="H42">
+        <v>79</v>
+      </c>
+      <c r="I42">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <v>46305</v>
+      </c>
+      <c r="B43">
+        <v>6</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" s="2">
+        <v>5</v>
+      </c>
+      <c r="F43" s="2">
+        <v>2020161</v>
+      </c>
+      <c r="G43" s="5">
+        <v>101.5</v>
+      </c>
+      <c r="H43">
+        <v>78</v>
+      </c>
+      <c r="I43">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
+        <v>46305</v>
+      </c>
+      <c r="B44">
+        <v>6</v>
+      </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
+      <c r="D44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E44" s="2">
+        <v>5</v>
+      </c>
+      <c r="F44" s="2">
+        <v>2480910</v>
+      </c>
+      <c r="G44" s="5">
+        <v>100.4</v>
+      </c>
+      <c r="H44">
+        <v>47</v>
+      </c>
+      <c r="I44">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
+        <v>46305</v>
+      </c>
+      <c r="B45">
+        <v>6</v>
+      </c>
+      <c r="C45">
+        <v>4</v>
+      </c>
+      <c r="D45" t="s">
+        <v>29</v>
+      </c>
+      <c r="E45" s="2">
+        <v>5</v>
+      </c>
+      <c r="F45" s="2">
+        <v>3122470</v>
+      </c>
+      <c r="G45" s="5">
+        <v>99.4</v>
+      </c>
+      <c r="H45">
+        <v>65</v>
+      </c>
+      <c r="I45">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
+        <v>46305</v>
+      </c>
+      <c r="B46">
+        <v>6</v>
+      </c>
+      <c r="C46">
+        <v>5</v>
+      </c>
+      <c r="D46" t="s">
+        <v>31</v>
+      </c>
+      <c r="E46" s="2">
+        <v>5</v>
+      </c>
+      <c r="F46" s="2">
+        <v>3876191</v>
+      </c>
+      <c r="G46" s="5">
+        <v>99.8</v>
+      </c>
+      <c r="H46">
+        <v>51</v>
+      </c>
+      <c r="I46">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
+        <v>46305</v>
+      </c>
+      <c r="B47">
+        <v>6</v>
+      </c>
+      <c r="C47">
+        <v>6</v>
+      </c>
+      <c r="D47" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="2">
+        <v>3</v>
+      </c>
+      <c r="F47" s="2">
+        <v>3923733</v>
+      </c>
+      <c r="G47" s="5">
+        <v>99.5</v>
+      </c>
+      <c r="H47">
+        <v>54</v>
+      </c>
+      <c r="I47">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
+        <v>46305</v>
+      </c>
+      <c r="B48">
+        <v>6</v>
+      </c>
+      <c r="C48">
+        <v>7</v>
+      </c>
+      <c r="D48" t="s">
+        <v>26</v>
+      </c>
+      <c r="E48" s="2">
+        <v>3</v>
+      </c>
+      <c r="F48" s="2">
+        <v>4617328</v>
+      </c>
+      <c r="G48" s="5">
+        <v>99.4</v>
+      </c>
+      <c r="H48">
+        <v>46</v>
+      </c>
+      <c r="I48">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <v>46305</v>
+      </c>
+      <c r="B49">
+        <v>6</v>
+      </c>
+      <c r="C49">
+        <v>8</v>
+      </c>
+      <c r="D49" t="s">
+        <v>27</v>
+      </c>
+      <c r="E49" s="2">
+        <v>4</v>
+      </c>
+      <c r="F49" s="2">
+        <v>5457445</v>
+      </c>
+      <c r="G49" s="5">
+        <v>102.1</v>
+      </c>
+      <c r="H49">
+        <v>51</v>
+      </c>
+      <c r="I49">
+        <v>346</v>
+      </c>
+    </row>
     <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <conditionalFormatting sqref="A2:J41">
-    <cfRule type="expression" dxfId="3" priority="1">
+  <conditionalFormatting sqref="A2:J49">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>MOD($B2, 2) = 1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>MOD($B2, 2) = 0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2710,7 +3081,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A820DAB-6033-4E1A-86E6-3C9D8203F219}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4492,6 +4863,357 @@
       </c>
       <c r="G76" s="1">
         <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>6</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>88</v>
+      </c>
+      <c r="D77" t="s">
+        <v>39</v>
+      </c>
+      <c r="E77" t="s">
+        <v>128</v>
+      </c>
+      <c r="F77">
+        <v>3</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>6</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+      <c r="C78" t="s">
+        <v>189</v>
+      </c>
+      <c r="D78" t="s">
+        <v>223</v>
+      </c>
+      <c r="E78" t="s">
+        <v>128</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>6</v>
+      </c>
+      <c r="B79">
+        <v>3</v>
+      </c>
+      <c r="C79" t="s">
+        <v>192</v>
+      </c>
+      <c r="D79" t="s">
+        <v>41</v>
+      </c>
+      <c r="E79" t="s">
+        <v>128</v>
+      </c>
+      <c r="F79">
+        <v>3</v>
+      </c>
+      <c r="G79" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>6</v>
+      </c>
+      <c r="B80">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>35</v>
+      </c>
+      <c r="D80" t="s">
+        <v>39</v>
+      </c>
+      <c r="E80" t="s">
+        <v>148</v>
+      </c>
+      <c r="F80">
+        <v>9</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>6</v>
+      </c>
+      <c r="B81">
+        <v>5</v>
+      </c>
+      <c r="C81" t="s">
+        <v>84</v>
+      </c>
+      <c r="D81" t="s">
+        <v>212</v>
+      </c>
+      <c r="E81" t="s">
+        <v>128</v>
+      </c>
+      <c r="F81">
+        <v>6</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>6</v>
+      </c>
+      <c r="B82">
+        <v>6</v>
+      </c>
+      <c r="C82" t="s">
+        <v>44</v>
+      </c>
+      <c r="D82" t="s">
+        <v>60</v>
+      </c>
+      <c r="E82" t="s">
+        <v>128</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0</v>
+      </c>
+      <c r="H82" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>6</v>
+      </c>
+      <c r="B83">
+        <v>7</v>
+      </c>
+      <c r="C83" t="s">
+        <v>96</v>
+      </c>
+      <c r="D83" t="s">
+        <v>50</v>
+      </c>
+      <c r="E83" t="s">
+        <v>265</v>
+      </c>
+      <c r="F83">
+        <v>8</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>6</v>
+      </c>
+      <c r="B84">
+        <v>8</v>
+      </c>
+      <c r="C84" t="s">
+        <v>283</v>
+      </c>
+      <c r="D84" t="s">
+        <v>39</v>
+      </c>
+      <c r="E84" t="s">
+        <v>128</v>
+      </c>
+      <c r="F84">
+        <v>4</v>
+      </c>
+      <c r="G84" s="1">
+        <v>2</v>
+      </c>
+      <c r="H84" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>6</v>
+      </c>
+      <c r="B85">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s">
+        <v>190</v>
+      </c>
+      <c r="D85" t="s">
+        <v>215</v>
+      </c>
+      <c r="E85" t="s">
+        <v>149</v>
+      </c>
+      <c r="F85">
+        <v>2</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>6</v>
+      </c>
+      <c r="B86">
+        <v>10</v>
+      </c>
+      <c r="C86" t="s">
+        <v>252</v>
+      </c>
+      <c r="D86" t="s">
+        <v>135</v>
+      </c>
+      <c r="E86" t="s">
+        <v>267</v>
+      </c>
+      <c r="F86">
+        <v>2</v>
+      </c>
+      <c r="G86" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>6</v>
+      </c>
+      <c r="B87">
+        <v>11</v>
+      </c>
+      <c r="C87" t="s">
+        <v>51</v>
+      </c>
+      <c r="D87" t="s">
+        <v>50</v>
+      </c>
+      <c r="E87" t="s">
+        <v>267</v>
+      </c>
+      <c r="F87">
+        <v>12</v>
+      </c>
+      <c r="G87" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>6</v>
+      </c>
+      <c r="B88">
+        <v>12</v>
+      </c>
+      <c r="C88" t="s">
+        <v>187</v>
+      </c>
+      <c r="D88" t="s">
+        <v>223</v>
+      </c>
+      <c r="E88" t="s">
+        <v>128</v>
+      </c>
+      <c r="F88">
+        <v>2</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>6</v>
+      </c>
+      <c r="B89">
+        <v>13</v>
+      </c>
+      <c r="C89" t="s">
+        <v>173</v>
+      </c>
+      <c r="D89" t="s">
+        <v>139</v>
+      </c>
+      <c r="E89" t="s">
+        <v>128</v>
+      </c>
+      <c r="F89">
+        <v>10</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>6</v>
+      </c>
+      <c r="B90">
+        <v>14</v>
+      </c>
+      <c r="C90" t="s">
+        <v>188</v>
+      </c>
+      <c r="D90" t="s">
+        <v>139</v>
+      </c>
+      <c r="E90" t="s">
+        <v>284</v>
+      </c>
+      <c r="F90">
+        <v>4</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>6</v>
+      </c>
+      <c r="B91">
+        <v>15</v>
+      </c>
+      <c r="C91" t="s">
+        <v>250</v>
+      </c>
+      <c r="D91" t="s">
+        <v>78</v>
+      </c>
+      <c r="E91" t="s">
+        <v>151</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4513,7 +5235,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330229B3-0B25-4B18-9D20-120CB711B0FB}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -4985,6 +5707,206 @@
         <v>1</v>
       </c>
     </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>254</v>
+      </c>
+      <c r="G24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>6</v>
+      </c>
+      <c r="B25" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" t="s">
+        <v>255</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>256</v>
+      </c>
+      <c r="G25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>6</v>
+      </c>
+      <c r="B26" t="s">
+        <v>206</v>
+      </c>
+      <c r="C26" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
+        <v>257</v>
+      </c>
+      <c r="G26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>6</v>
+      </c>
+      <c r="B27" t="s">
+        <v>206</v>
+      </c>
+      <c r="C27" t="s">
+        <v>195</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="F27" t="s">
+        <v>258</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>6</v>
+      </c>
+      <c r="B28" t="s">
+        <v>211</v>
+      </c>
+      <c r="C28" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="F28" t="s">
+        <v>232</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>6</v>
+      </c>
+      <c r="B29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C29" t="s">
+        <v>259</v>
+      </c>
+      <c r="D29">
+        <v>6</v>
+      </c>
+      <c r="F29" t="s">
+        <v>254</v>
+      </c>
+      <c r="G29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>6</v>
+      </c>
+      <c r="B30" t="s">
+        <v>263</v>
+      </c>
+      <c r="C30" t="s">
+        <v>260</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="F30" t="s">
+        <v>261</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>6</v>
+      </c>
+      <c r="B31" t="s">
+        <v>263</v>
+      </c>
+      <c r="C31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="F31" t="s">
+        <v>262</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>6</v>
+      </c>
+      <c r="B32" t="s">
+        <v>263</v>
+      </c>
+      <c r="C32" t="s">
+        <v>193</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
+        <v>194</v>
+      </c>
+      <c r="G32">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>6</v>
+      </c>
+      <c r="B33" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="F33" t="s">
+        <v>264</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -4995,7 +5917,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BFE37CD-4558-41F4-92EA-FE7453319710}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -6786,6 +7708,357 @@
         <v>0</v>
       </c>
     </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>6</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>88</v>
+      </c>
+      <c r="D77" t="s">
+        <v>39</v>
+      </c>
+      <c r="E77" t="s">
+        <v>128</v>
+      </c>
+      <c r="F77" s="3">
+        <v>3</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>6</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+      <c r="C78" t="s">
+        <v>35</v>
+      </c>
+      <c r="D78" t="s">
+        <v>39</v>
+      </c>
+      <c r="E78" t="s">
+        <v>148</v>
+      </c>
+      <c r="F78" s="3">
+        <v>9</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>6</v>
+      </c>
+      <c r="B79">
+        <v>3</v>
+      </c>
+      <c r="C79" t="s">
+        <v>219</v>
+      </c>
+      <c r="D79" t="s">
+        <v>215</v>
+      </c>
+      <c r="E79" t="s">
+        <v>128</v>
+      </c>
+      <c r="F79" s="3">
+        <v>8</v>
+      </c>
+      <c r="G79" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>6</v>
+      </c>
+      <c r="B80">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>79</v>
+      </c>
+      <c r="D80" t="s">
+        <v>39</v>
+      </c>
+      <c r="E80" t="s">
+        <v>128</v>
+      </c>
+      <c r="F80" s="3">
+        <v>4</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>6</v>
+      </c>
+      <c r="B81">
+        <v>5</v>
+      </c>
+      <c r="C81" t="s">
+        <v>214</v>
+      </c>
+      <c r="D81" t="s">
+        <v>50</v>
+      </c>
+      <c r="E81" t="s">
+        <v>184</v>
+      </c>
+      <c r="F81" s="3">
+        <v>9</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>6</v>
+      </c>
+      <c r="B82">
+        <v>6</v>
+      </c>
+      <c r="C82" t="s">
+        <v>96</v>
+      </c>
+      <c r="D82" t="s">
+        <v>50</v>
+      </c>
+      <c r="E82" t="s">
+        <v>265</v>
+      </c>
+      <c r="F82" s="3">
+        <v>8</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="H82" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>6</v>
+      </c>
+      <c r="B83">
+        <v>7</v>
+      </c>
+      <c r="C83" t="s">
+        <v>84</v>
+      </c>
+      <c r="D83" t="s">
+        <v>212</v>
+      </c>
+      <c r="E83" t="s">
+        <v>128</v>
+      </c>
+      <c r="F83" s="3">
+        <v>6</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>6</v>
+      </c>
+      <c r="B84">
+        <v>8</v>
+      </c>
+      <c r="C84" t="s">
+        <v>152</v>
+      </c>
+      <c r="D84" t="s">
+        <v>135</v>
+      </c>
+      <c r="E84" t="s">
+        <v>128</v>
+      </c>
+      <c r="F84" s="3">
+        <v>2</v>
+      </c>
+      <c r="G84" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>6</v>
+      </c>
+      <c r="B85">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s">
+        <v>217</v>
+      </c>
+      <c r="D85" t="s">
+        <v>41</v>
+      </c>
+      <c r="E85" t="s">
+        <v>151</v>
+      </c>
+      <c r="F85" s="3">
+        <v>6</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>6</v>
+      </c>
+      <c r="B86">
+        <v>10</v>
+      </c>
+      <c r="C86" t="s">
+        <v>49</v>
+      </c>
+      <c r="D86" t="s">
+        <v>139</v>
+      </c>
+      <c r="E86" t="s">
+        <v>266</v>
+      </c>
+      <c r="F86" s="3">
+        <v>12</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="H86" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>6</v>
+      </c>
+      <c r="B87">
+        <v>11</v>
+      </c>
+      <c r="C87" t="s">
+        <v>51</v>
+      </c>
+      <c r="D87" t="s">
+        <v>50</v>
+      </c>
+      <c r="E87" t="s">
+        <v>267</v>
+      </c>
+      <c r="F87" s="3">
+        <v>12</v>
+      </c>
+      <c r="G87" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>6</v>
+      </c>
+      <c r="B88">
+        <v>12</v>
+      </c>
+      <c r="C88" t="s">
+        <v>216</v>
+      </c>
+      <c r="D88" t="s">
+        <v>144</v>
+      </c>
+      <c r="E88" t="s">
+        <v>47</v>
+      </c>
+      <c r="F88" s="3">
+        <v>0</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>6</v>
+      </c>
+      <c r="B89">
+        <v>13</v>
+      </c>
+      <c r="C89" t="s">
+        <v>268</v>
+      </c>
+      <c r="D89" t="s">
+        <v>156</v>
+      </c>
+      <c r="E89" t="s">
+        <v>47</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>6</v>
+      </c>
+      <c r="B90">
+        <v>14</v>
+      </c>
+      <c r="C90" t="s">
+        <v>237</v>
+      </c>
+      <c r="D90" t="s">
+        <v>223</v>
+      </c>
+      <c r="E90" t="s">
+        <v>128</v>
+      </c>
+      <c r="F90" s="3">
+        <v>3</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>6</v>
+      </c>
+      <c r="B91">
+        <v>15</v>
+      </c>
+      <c r="C91" t="s">
+        <v>213</v>
+      </c>
+      <c r="D91" t="s">
+        <v>78</v>
+      </c>
+      <c r="E91" t="s">
+        <v>128</v>
+      </c>
+      <c r="F91" s="3">
+        <v>2</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6797,7 +8070,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A36F238-E413-4105-953D-9BEAF6AEF0DC}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
@@ -8584,6 +9857,357 @@
       </c>
       <c r="G76" s="1">
         <v>-0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>6</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>66</v>
+      </c>
+      <c r="D77" t="s">
+        <v>60</v>
+      </c>
+      <c r="E77" t="s">
+        <v>128</v>
+      </c>
+      <c r="F77" s="3">
+        <v>2</v>
+      </c>
+      <c r="G77" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>6</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+      <c r="C78" t="s">
+        <v>79</v>
+      </c>
+      <c r="D78" t="s">
+        <v>39</v>
+      </c>
+      <c r="E78" t="s">
+        <v>128</v>
+      </c>
+      <c r="F78" s="3">
+        <v>4</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>6</v>
+      </c>
+      <c r="B79">
+        <v>3</v>
+      </c>
+      <c r="C79" t="s">
+        <v>222</v>
+      </c>
+      <c r="D79" t="s">
+        <v>215</v>
+      </c>
+      <c r="E79" t="s">
+        <v>128</v>
+      </c>
+      <c r="F79" s="3">
+        <v>0</v>
+      </c>
+      <c r="G79" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>6</v>
+      </c>
+      <c r="B80">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>225</v>
+      </c>
+      <c r="D80" t="s">
+        <v>60</v>
+      </c>
+      <c r="E80" t="s">
+        <v>128</v>
+      </c>
+      <c r="F80" s="3">
+        <v>3</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>6</v>
+      </c>
+      <c r="B81">
+        <v>5</v>
+      </c>
+      <c r="C81" t="s">
+        <v>247</v>
+      </c>
+      <c r="D81" t="s">
+        <v>39</v>
+      </c>
+      <c r="E81" t="s">
+        <v>154</v>
+      </c>
+      <c r="F81" s="3">
+        <v>1</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>6</v>
+      </c>
+      <c r="B82">
+        <v>6</v>
+      </c>
+      <c r="C82" t="s">
+        <v>44</v>
+      </c>
+      <c r="D82" t="s">
+        <v>60</v>
+      </c>
+      <c r="E82" t="s">
+        <v>128</v>
+      </c>
+      <c r="F82" s="3">
+        <v>2</v>
+      </c>
+      <c r="G82" s="1">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="H82" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>6</v>
+      </c>
+      <c r="B83">
+        <v>7</v>
+      </c>
+      <c r="C83" t="s">
+        <v>214</v>
+      </c>
+      <c r="D83" t="s">
+        <v>50</v>
+      </c>
+      <c r="E83" t="s">
+        <v>184</v>
+      </c>
+      <c r="F83" s="3">
+        <v>9</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H83" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>6</v>
+      </c>
+      <c r="B84">
+        <v>8</v>
+      </c>
+      <c r="C84" t="s">
+        <v>84</v>
+      </c>
+      <c r="D84" t="s">
+        <v>212</v>
+      </c>
+      <c r="E84" t="s">
+        <v>128</v>
+      </c>
+      <c r="F84" s="3">
+        <v>6</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>6</v>
+      </c>
+      <c r="B85">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s">
+        <v>51</v>
+      </c>
+      <c r="D85" t="s">
+        <v>50</v>
+      </c>
+      <c r="E85" t="s">
+        <v>267</v>
+      </c>
+      <c r="F85" s="3">
+        <v>12</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>6</v>
+      </c>
+      <c r="B86">
+        <v>10</v>
+      </c>
+      <c r="C86" t="s">
+        <v>49</v>
+      </c>
+      <c r="D86" t="s">
+        <v>139</v>
+      </c>
+      <c r="E86" t="s">
+        <v>266</v>
+      </c>
+      <c r="F86" s="3">
+        <v>6</v>
+      </c>
+      <c r="G86" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>6</v>
+      </c>
+      <c r="B87">
+        <v>11</v>
+      </c>
+      <c r="C87" t="s">
+        <v>217</v>
+      </c>
+      <c r="D87" t="s">
+        <v>41</v>
+      </c>
+      <c r="E87" t="s">
+        <v>151</v>
+      </c>
+      <c r="F87" s="3">
+        <v>6</v>
+      </c>
+      <c r="G87" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>6</v>
+      </c>
+      <c r="B88">
+        <v>12</v>
+      </c>
+      <c r="C88" t="s">
+        <v>32</v>
+      </c>
+      <c r="D88" t="s">
+        <v>212</v>
+      </c>
+      <c r="E88" t="s">
+        <v>128</v>
+      </c>
+      <c r="F88" s="3">
+        <v>9</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>6</v>
+      </c>
+      <c r="B89">
+        <v>13</v>
+      </c>
+      <c r="C89" t="s">
+        <v>69</v>
+      </c>
+      <c r="D89" t="s">
+        <v>140</v>
+      </c>
+      <c r="E89" t="s">
+        <v>128</v>
+      </c>
+      <c r="F89" s="3">
+        <v>3</v>
+      </c>
+      <c r="G89" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>6</v>
+      </c>
+      <c r="B90">
+        <v>14</v>
+      </c>
+      <c r="C90" t="s">
+        <v>77</v>
+      </c>
+      <c r="D90" t="s">
+        <v>127</v>
+      </c>
+      <c r="E90" t="s">
+        <v>128</v>
+      </c>
+      <c r="F90" s="3">
+        <v>6</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>6</v>
+      </c>
+      <c r="B91">
+        <v>15</v>
+      </c>
+      <c r="C91" t="s">
+        <v>59</v>
+      </c>
+      <c r="D91" t="s">
+        <v>129</v>
+      </c>
+      <c r="E91" t="s">
+        <v>269</v>
+      </c>
+      <c r="F91" s="3">
+        <v>1</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8596,7 +10220,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0779779-8AAD-4A05-B64B-AAE55E86E147}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
@@ -10382,6 +12006,357 @@
         <v>1</v>
       </c>
       <c r="G76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>6</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>180</v>
+      </c>
+      <c r="D77" t="s">
+        <v>75</v>
+      </c>
+      <c r="E77" t="s">
+        <v>128</v>
+      </c>
+      <c r="F77" s="3">
+        <v>2</v>
+      </c>
+      <c r="G77" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>6</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+      <c r="C78" t="s">
+        <v>35</v>
+      </c>
+      <c r="D78" t="s">
+        <v>39</v>
+      </c>
+      <c r="E78" t="s">
+        <v>148</v>
+      </c>
+      <c r="F78" s="3">
+        <v>9</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>6</v>
+      </c>
+      <c r="B79">
+        <v>3</v>
+      </c>
+      <c r="C79" t="s">
+        <v>38</v>
+      </c>
+      <c r="D79" t="s">
+        <v>135</v>
+      </c>
+      <c r="E79" t="s">
+        <v>128</v>
+      </c>
+      <c r="F79" s="3">
+        <v>1</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>6</v>
+      </c>
+      <c r="B80">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>270</v>
+      </c>
+      <c r="D80" t="s">
+        <v>75</v>
+      </c>
+      <c r="E80" t="s">
+        <v>128</v>
+      </c>
+      <c r="F80" s="3">
+        <v>3</v>
+      </c>
+      <c r="G80" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>6</v>
+      </c>
+      <c r="B81">
+        <v>5</v>
+      </c>
+      <c r="C81" t="s">
+        <v>79</v>
+      </c>
+      <c r="D81" t="s">
+        <v>39</v>
+      </c>
+      <c r="E81" t="s">
+        <v>128</v>
+      </c>
+      <c r="F81" s="3">
+        <v>4</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>6</v>
+      </c>
+      <c r="B82">
+        <v>6</v>
+      </c>
+      <c r="C82" t="s">
+        <v>44</v>
+      </c>
+      <c r="D82" t="s">
+        <v>60</v>
+      </c>
+      <c r="E82" t="s">
+        <v>128</v>
+      </c>
+      <c r="F82" s="3">
+        <v>2</v>
+      </c>
+      <c r="G82" s="1">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="H82" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>6</v>
+      </c>
+      <c r="B83">
+        <v>7</v>
+      </c>
+      <c r="C83" t="s">
+        <v>84</v>
+      </c>
+      <c r="D83" t="s">
+        <v>212</v>
+      </c>
+      <c r="E83" t="s">
+        <v>128</v>
+      </c>
+      <c r="F83" s="3">
+        <v>6</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>6</v>
+      </c>
+      <c r="B84">
+        <v>8</v>
+      </c>
+      <c r="C84" t="s">
+        <v>214</v>
+      </c>
+      <c r="D84" t="s">
+        <v>50</v>
+      </c>
+      <c r="E84" t="s">
+        <v>184</v>
+      </c>
+      <c r="F84" s="3">
+        <v>9</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>6</v>
+      </c>
+      <c r="B85">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s">
+        <v>80</v>
+      </c>
+      <c r="D85" t="s">
+        <v>139</v>
+      </c>
+      <c r="E85" t="s">
+        <v>128</v>
+      </c>
+      <c r="F85" s="3">
+        <v>3</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>6</v>
+      </c>
+      <c r="B86">
+        <v>10</v>
+      </c>
+      <c r="C86" t="s">
+        <v>271</v>
+      </c>
+      <c r="D86" t="s">
+        <v>78</v>
+      </c>
+      <c r="E86" t="s">
+        <v>128</v>
+      </c>
+      <c r="F86" s="3">
+        <v>2</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>6</v>
+      </c>
+      <c r="B87">
+        <v>11</v>
+      </c>
+      <c r="C87" t="s">
+        <v>49</v>
+      </c>
+      <c r="D87" t="s">
+        <v>139</v>
+      </c>
+      <c r="E87" t="s">
+        <v>266</v>
+      </c>
+      <c r="F87" s="3">
+        <v>6</v>
+      </c>
+      <c r="G87" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="H87" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>6</v>
+      </c>
+      <c r="B88">
+        <v>12</v>
+      </c>
+      <c r="C88" t="s">
+        <v>32</v>
+      </c>
+      <c r="D88" t="s">
+        <v>212</v>
+      </c>
+      <c r="E88" t="s">
+        <v>128</v>
+      </c>
+      <c r="F88" s="3">
+        <v>9</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>6</v>
+      </c>
+      <c r="B89">
+        <v>13</v>
+      </c>
+      <c r="C89" t="s">
+        <v>272</v>
+      </c>
+      <c r="D89" t="s">
+        <v>156</v>
+      </c>
+      <c r="E89" t="s">
+        <v>47</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>6</v>
+      </c>
+      <c r="B90">
+        <v>14</v>
+      </c>
+      <c r="C90" t="s">
+        <v>87</v>
+      </c>
+      <c r="D90" t="s">
+        <v>127</v>
+      </c>
+      <c r="E90" t="s">
+        <v>128</v>
+      </c>
+      <c r="F90" s="3">
+        <v>4</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>6</v>
+      </c>
+      <c r="B91">
+        <v>15</v>
+      </c>
+      <c r="C91" t="s">
+        <v>226</v>
+      </c>
+      <c r="D91" t="s">
+        <v>127</v>
+      </c>
+      <c r="E91" t="s">
+        <v>273</v>
+      </c>
+      <c r="F91" s="3">
+        <v>6</v>
+      </c>
+      <c r="G91" s="1">
         <v>0</v>
       </c>
     </row>
@@ -10395,7 +12370,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{079AB974-BCF6-45DE-BAD2-52D6AC42558C}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
@@ -12186,6 +14161,357 @@
         <v>0</v>
       </c>
     </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>6</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>88</v>
+      </c>
+      <c r="D77" t="s">
+        <v>39</v>
+      </c>
+      <c r="E77" t="s">
+        <v>128</v>
+      </c>
+      <c r="F77">
+        <v>3</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>6</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+      <c r="C78" t="s">
+        <v>89</v>
+      </c>
+      <c r="D78" t="s">
+        <v>39</v>
+      </c>
+      <c r="E78" t="s">
+        <v>128</v>
+      </c>
+      <c r="F78">
+        <v>4</v>
+      </c>
+      <c r="G78" s="1">
+        <v>2</v>
+      </c>
+      <c r="H78" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>6</v>
+      </c>
+      <c r="B79">
+        <v>3</v>
+      </c>
+      <c r="C79" t="s">
+        <v>90</v>
+      </c>
+      <c r="D79" t="s">
+        <v>156</v>
+      </c>
+      <c r="E79" t="s">
+        <v>128</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>6</v>
+      </c>
+      <c r="B80">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>225</v>
+      </c>
+      <c r="D80" t="s">
+        <v>60</v>
+      </c>
+      <c r="E80" t="s">
+        <v>128</v>
+      </c>
+      <c r="F80">
+        <v>3</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>6</v>
+      </c>
+      <c r="B81">
+        <v>5</v>
+      </c>
+      <c r="C81" t="s">
+        <v>40</v>
+      </c>
+      <c r="D81" t="s">
+        <v>60</v>
+      </c>
+      <c r="E81" t="s">
+        <v>128</v>
+      </c>
+      <c r="F81">
+        <v>2</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>6</v>
+      </c>
+      <c r="B82">
+        <v>6</v>
+      </c>
+      <c r="C82" t="s">
+        <v>214</v>
+      </c>
+      <c r="D82" t="s">
+        <v>50</v>
+      </c>
+      <c r="E82" t="s">
+        <v>184</v>
+      </c>
+      <c r="F82">
+        <v>9</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>6</v>
+      </c>
+      <c r="B83">
+        <v>7</v>
+      </c>
+      <c r="C83" t="s">
+        <v>274</v>
+      </c>
+      <c r="D83" t="s">
+        <v>75</v>
+      </c>
+      <c r="E83" t="s">
+        <v>275</v>
+      </c>
+      <c r="F83">
+        <v>2</v>
+      </c>
+      <c r="G83" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>6</v>
+      </c>
+      <c r="B84">
+        <v>8</v>
+      </c>
+      <c r="C84" t="s">
+        <v>80</v>
+      </c>
+      <c r="D84" t="s">
+        <v>139</v>
+      </c>
+      <c r="E84" t="s">
+        <v>128</v>
+      </c>
+      <c r="F84">
+        <v>3</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>6</v>
+      </c>
+      <c r="B85">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s">
+        <v>51</v>
+      </c>
+      <c r="D85" t="s">
+        <v>50</v>
+      </c>
+      <c r="E85" t="s">
+        <v>267</v>
+      </c>
+      <c r="F85">
+        <v>12</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>6</v>
+      </c>
+      <c r="B86">
+        <v>10</v>
+      </c>
+      <c r="C86" t="s">
+        <v>53</v>
+      </c>
+      <c r="D86" t="s">
+        <v>78</v>
+      </c>
+      <c r="E86" t="s">
+        <v>128</v>
+      </c>
+      <c r="F86">
+        <v>2</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>6</v>
+      </c>
+      <c r="B87">
+        <v>11</v>
+      </c>
+      <c r="C87" t="s">
+        <v>49</v>
+      </c>
+      <c r="D87" t="s">
+        <v>139</v>
+      </c>
+      <c r="E87" t="s">
+        <v>266</v>
+      </c>
+      <c r="F87">
+        <v>6</v>
+      </c>
+      <c r="G87" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="H87" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>6</v>
+      </c>
+      <c r="B88">
+        <v>12</v>
+      </c>
+      <c r="C88" t="s">
+        <v>91</v>
+      </c>
+      <c r="D88" t="s">
+        <v>140</v>
+      </c>
+      <c r="E88" t="s">
+        <v>47</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>6</v>
+      </c>
+      <c r="B89">
+        <v>13</v>
+      </c>
+      <c r="C89" t="s">
+        <v>93</v>
+      </c>
+      <c r="D89" t="s">
+        <v>136</v>
+      </c>
+      <c r="E89" t="s">
+        <v>128</v>
+      </c>
+      <c r="F89">
+        <v>2</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>6</v>
+      </c>
+      <c r="B90">
+        <v>14</v>
+      </c>
+      <c r="C90" t="s">
+        <v>276</v>
+      </c>
+      <c r="D90" t="s">
+        <v>212</v>
+      </c>
+      <c r="E90" t="s">
+        <v>277</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>6</v>
+      </c>
+      <c r="B91">
+        <v>15</v>
+      </c>
+      <c r="C91" t="s">
+        <v>94</v>
+      </c>
+      <c r="D91" t="s">
+        <v>129</v>
+      </c>
+      <c r="E91" t="s">
+        <v>128</v>
+      </c>
+      <c r="F91">
+        <v>6</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -12196,7 +14522,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B6E11CD-9E90-4D11-92A8-D8C539D81231}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="29.28515625" customWidth="1"/>
@@ -13980,6 +16306,357 @@
         <v>2</v>
       </c>
       <c r="G76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>6</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>55</v>
+      </c>
+      <c r="D77" t="s">
+        <v>140</v>
+      </c>
+      <c r="E77" t="s">
+        <v>128</v>
+      </c>
+      <c r="F77">
+        <v>3</v>
+      </c>
+      <c r="G77" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>6</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+      <c r="C78" t="s">
+        <v>35</v>
+      </c>
+      <c r="D78" t="s">
+        <v>39</v>
+      </c>
+      <c r="E78" t="s">
+        <v>148</v>
+      </c>
+      <c r="F78">
+        <v>9</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>6</v>
+      </c>
+      <c r="B79">
+        <v>3</v>
+      </c>
+      <c r="C79" t="s">
+        <v>40</v>
+      </c>
+      <c r="D79" t="s">
+        <v>60</v>
+      </c>
+      <c r="E79" t="s">
+        <v>128</v>
+      </c>
+      <c r="F79">
+        <v>2</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>6</v>
+      </c>
+      <c r="B80">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>69</v>
+      </c>
+      <c r="D80" t="s">
+        <v>140</v>
+      </c>
+      <c r="E80" t="s">
+        <v>128</v>
+      </c>
+      <c r="F80">
+        <v>3</v>
+      </c>
+      <c r="G80" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>6</v>
+      </c>
+      <c r="B81">
+        <v>5</v>
+      </c>
+      <c r="C81" t="s">
+        <v>229</v>
+      </c>
+      <c r="D81" t="s">
+        <v>212</v>
+      </c>
+      <c r="E81" t="s">
+        <v>278</v>
+      </c>
+      <c r="F81">
+        <v>15</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>6</v>
+      </c>
+      <c r="B82">
+        <v>6</v>
+      </c>
+      <c r="C82" t="s">
+        <v>57</v>
+      </c>
+      <c r="D82" t="s">
+        <v>212</v>
+      </c>
+      <c r="E82" t="s">
+        <v>265</v>
+      </c>
+      <c r="F82">
+        <v>5</v>
+      </c>
+      <c r="G82" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>6</v>
+      </c>
+      <c r="B83">
+        <v>7</v>
+      </c>
+      <c r="C83" t="s">
+        <v>96</v>
+      </c>
+      <c r="D83" t="s">
+        <v>50</v>
+      </c>
+      <c r="E83" t="s">
+        <v>265</v>
+      </c>
+      <c r="F83">
+        <v>8</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="H83" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>6</v>
+      </c>
+      <c r="B84">
+        <v>8</v>
+      </c>
+      <c r="C84" t="s">
+        <v>279</v>
+      </c>
+      <c r="D84" t="s">
+        <v>223</v>
+      </c>
+      <c r="E84" t="s">
+        <v>181</v>
+      </c>
+      <c r="F84">
+        <v>6</v>
+      </c>
+      <c r="G84" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>6</v>
+      </c>
+      <c r="B85">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s">
+        <v>44</v>
+      </c>
+      <c r="D85" t="s">
+        <v>60</v>
+      </c>
+      <c r="E85" t="s">
+        <v>128</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>6</v>
+      </c>
+      <c r="B86">
+        <v>10</v>
+      </c>
+      <c r="C86" t="s">
+        <v>49</v>
+      </c>
+      <c r="D86" t="s">
+        <v>139</v>
+      </c>
+      <c r="E86" t="s">
+        <v>266</v>
+      </c>
+      <c r="F86">
+        <v>12</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="H86" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>6</v>
+      </c>
+      <c r="B87">
+        <v>11</v>
+      </c>
+      <c r="C87" t="s">
+        <v>280</v>
+      </c>
+      <c r="D87" t="s">
+        <v>212</v>
+      </c>
+      <c r="E87" t="s">
+        <v>281</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>6</v>
+      </c>
+      <c r="B88">
+        <v>12</v>
+      </c>
+      <c r="C88" t="s">
+        <v>96</v>
+      </c>
+      <c r="D88" t="s">
+        <v>144</v>
+      </c>
+      <c r="E88" t="s">
+        <v>47</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>6</v>
+      </c>
+      <c r="B89">
+        <v>13</v>
+      </c>
+      <c r="C89" t="s">
+        <v>272</v>
+      </c>
+      <c r="D89" t="s">
+        <v>156</v>
+      </c>
+      <c r="E89" t="s">
+        <v>47</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>6</v>
+      </c>
+      <c r="B90">
+        <v>14</v>
+      </c>
+      <c r="C90" t="s">
+        <v>53</v>
+      </c>
+      <c r="D90" t="s">
+        <v>78</v>
+      </c>
+      <c r="E90" t="s">
+        <v>128</v>
+      </c>
+      <c r="F90">
+        <v>2</v>
+      </c>
+      <c r="G90" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>6</v>
+      </c>
+      <c r="B91">
+        <v>15</v>
+      </c>
+      <c r="C91" t="s">
+        <v>62</v>
+      </c>
+      <c r="D91" t="s">
+        <v>144</v>
+      </c>
+      <c r="E91" t="s">
+        <v>128</v>
+      </c>
+      <c r="F91">
+        <v>11</v>
+      </c>
+      <c r="G91" s="1">
         <v>0</v>
       </c>
     </row>
@@ -13993,7 +16670,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222824F9-1AC4-4931-8973-86755A3F1C37}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -15775,6 +18452,357 @@
       </c>
       <c r="G76" s="1">
         <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>6</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>88</v>
+      </c>
+      <c r="D77" t="s">
+        <v>39</v>
+      </c>
+      <c r="E77" t="s">
+        <v>128</v>
+      </c>
+      <c r="F77">
+        <v>3</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>6</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+      <c r="C78" t="s">
+        <v>35</v>
+      </c>
+      <c r="D78" t="s">
+        <v>39</v>
+      </c>
+      <c r="E78" t="s">
+        <v>148</v>
+      </c>
+      <c r="F78">
+        <v>9</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>6</v>
+      </c>
+      <c r="B79">
+        <v>3</v>
+      </c>
+      <c r="C79" t="s">
+        <v>229</v>
+      </c>
+      <c r="D79" t="s">
+        <v>212</v>
+      </c>
+      <c r="E79" t="s">
+        <v>278</v>
+      </c>
+      <c r="F79">
+        <v>15</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>6</v>
+      </c>
+      <c r="B80">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>38</v>
+      </c>
+      <c r="D80" t="s">
+        <v>135</v>
+      </c>
+      <c r="E80" t="s">
+        <v>128</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>6</v>
+      </c>
+      <c r="B81">
+        <v>5</v>
+      </c>
+      <c r="C81" t="s">
+        <v>214</v>
+      </c>
+      <c r="D81" t="s">
+        <v>50</v>
+      </c>
+      <c r="E81" t="s">
+        <v>184</v>
+      </c>
+      <c r="F81">
+        <v>18</v>
+      </c>
+      <c r="G81" s="1">
+        <v>1.43</v>
+      </c>
+      <c r="H81" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>6</v>
+      </c>
+      <c r="B82">
+        <v>6</v>
+      </c>
+      <c r="C82" t="s">
+        <v>44</v>
+      </c>
+      <c r="D82" t="s">
+        <v>60</v>
+      </c>
+      <c r="E82" t="s">
+        <v>128</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>6</v>
+      </c>
+      <c r="B83">
+        <v>7</v>
+      </c>
+      <c r="C83" t="s">
+        <v>84</v>
+      </c>
+      <c r="D83" t="s">
+        <v>212</v>
+      </c>
+      <c r="E83" t="s">
+        <v>128</v>
+      </c>
+      <c r="F83">
+        <v>6</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="H83" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>6</v>
+      </c>
+      <c r="B84">
+        <v>8</v>
+      </c>
+      <c r="C84" t="s">
+        <v>247</v>
+      </c>
+      <c r="D84" t="s">
+        <v>39</v>
+      </c>
+      <c r="E84" t="s">
+        <v>154</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>6</v>
+      </c>
+      <c r="B85">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s">
+        <v>217</v>
+      </c>
+      <c r="D85" t="s">
+        <v>41</v>
+      </c>
+      <c r="E85" t="s">
+        <v>151</v>
+      </c>
+      <c r="F85">
+        <v>6</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>6</v>
+      </c>
+      <c r="B86">
+        <v>10</v>
+      </c>
+      <c r="C86" t="s">
+        <v>51</v>
+      </c>
+      <c r="D86" t="s">
+        <v>50</v>
+      </c>
+      <c r="E86" t="s">
+        <v>267</v>
+      </c>
+      <c r="F86">
+        <v>12</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>6</v>
+      </c>
+      <c r="B87">
+        <v>11</v>
+      </c>
+      <c r="C87" t="s">
+        <v>49</v>
+      </c>
+      <c r="D87" t="s">
+        <v>139</v>
+      </c>
+      <c r="E87" t="s">
+        <v>266</v>
+      </c>
+      <c r="F87">
+        <v>6</v>
+      </c>
+      <c r="G87" s="1">
+        <v>-0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>6</v>
+      </c>
+      <c r="B88">
+        <v>12</v>
+      </c>
+      <c r="C88" t="s">
+        <v>96</v>
+      </c>
+      <c r="D88" t="s">
+        <v>144</v>
+      </c>
+      <c r="E88" t="s">
+        <v>47</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>6</v>
+      </c>
+      <c r="B89">
+        <v>13</v>
+      </c>
+      <c r="C89" t="s">
+        <v>57</v>
+      </c>
+      <c r="D89" t="s">
+        <v>212</v>
+      </c>
+      <c r="E89" t="s">
+        <v>265</v>
+      </c>
+      <c r="F89">
+        <v>5</v>
+      </c>
+      <c r="G89" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>6</v>
+      </c>
+      <c r="B90">
+        <v>14</v>
+      </c>
+      <c r="C90" t="s">
+        <v>191</v>
+      </c>
+      <c r="D90" t="s">
+        <v>129</v>
+      </c>
+      <c r="E90" t="s">
+        <v>128</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>6</v>
+      </c>
+      <c r="B91">
+        <v>15</v>
+      </c>
+      <c r="C91" t="s">
+        <v>189</v>
+      </c>
+      <c r="D91" t="s">
+        <v>223</v>
+      </c>
+      <c r="E91" t="s">
+        <v>128</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91" s="1">
+        <v>-0.14000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -15787,7 +18815,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB542D51-1B6E-4A6F-B385-F419919DC470}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -17571,6 +20599,357 @@
         <v>4</v>
       </c>
       <c r="G76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>6</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>88</v>
+      </c>
+      <c r="D77" t="s">
+        <v>39</v>
+      </c>
+      <c r="E77" t="s">
+        <v>128</v>
+      </c>
+      <c r="F77">
+        <v>3</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>6</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+      <c r="C78" t="s">
+        <v>79</v>
+      </c>
+      <c r="D78" t="s">
+        <v>39</v>
+      </c>
+      <c r="E78" t="s">
+        <v>128</v>
+      </c>
+      <c r="F78">
+        <v>4</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>6</v>
+      </c>
+      <c r="B79">
+        <v>3</v>
+      </c>
+      <c r="C79" t="s">
+        <v>104</v>
+      </c>
+      <c r="D79" t="s">
+        <v>139</v>
+      </c>
+      <c r="E79" t="s">
+        <v>128</v>
+      </c>
+      <c r="F79">
+        <v>6</v>
+      </c>
+      <c r="G79" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>6</v>
+      </c>
+      <c r="B80">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>225</v>
+      </c>
+      <c r="D80" t="s">
+        <v>60</v>
+      </c>
+      <c r="E80" t="s">
+        <v>128</v>
+      </c>
+      <c r="F80">
+        <v>3</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>6</v>
+      </c>
+      <c r="B81">
+        <v>5</v>
+      </c>
+      <c r="C81" t="s">
+        <v>282</v>
+      </c>
+      <c r="D81" t="s">
+        <v>156</v>
+      </c>
+      <c r="E81" t="s">
+        <v>265</v>
+      </c>
+      <c r="F81">
+        <v>3</v>
+      </c>
+      <c r="G81" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>6</v>
+      </c>
+      <c r="B82">
+        <v>6</v>
+      </c>
+      <c r="C82" t="s">
+        <v>44</v>
+      </c>
+      <c r="D82" t="s">
+        <v>60</v>
+      </c>
+      <c r="E82" t="s">
+        <v>128</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>6</v>
+      </c>
+      <c r="B83">
+        <v>7</v>
+      </c>
+      <c r="C83" t="s">
+        <v>147</v>
+      </c>
+      <c r="D83" t="s">
+        <v>139</v>
+      </c>
+      <c r="E83" t="s">
+        <v>128</v>
+      </c>
+      <c r="F83">
+        <v>6</v>
+      </c>
+      <c r="G83" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>6</v>
+      </c>
+      <c r="B84">
+        <v>8</v>
+      </c>
+      <c r="C84" t="s">
+        <v>100</v>
+      </c>
+      <c r="D84" t="s">
+        <v>136</v>
+      </c>
+      <c r="E84" t="s">
+        <v>224</v>
+      </c>
+      <c r="F84">
+        <v>2</v>
+      </c>
+      <c r="G84" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>6</v>
+      </c>
+      <c r="B85">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s">
+        <v>49</v>
+      </c>
+      <c r="D85" t="s">
+        <v>139</v>
+      </c>
+      <c r="E85" t="s">
+        <v>266</v>
+      </c>
+      <c r="F85">
+        <v>12</v>
+      </c>
+      <c r="G85" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="H85" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>6</v>
+      </c>
+      <c r="B86">
+        <v>10</v>
+      </c>
+      <c r="C86" t="s">
+        <v>51</v>
+      </c>
+      <c r="D86" t="s">
+        <v>50</v>
+      </c>
+      <c r="E86" t="s">
+        <v>267</v>
+      </c>
+      <c r="F86">
+        <v>12</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>6</v>
+      </c>
+      <c r="B87">
+        <v>11</v>
+      </c>
+      <c r="C87" t="s">
+        <v>190</v>
+      </c>
+      <c r="D87" t="s">
+        <v>215</v>
+      </c>
+      <c r="E87" t="s">
+        <v>149</v>
+      </c>
+      <c r="F87">
+        <v>2</v>
+      </c>
+      <c r="G87" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="H87" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>6</v>
+      </c>
+      <c r="B88">
+        <v>12</v>
+      </c>
+      <c r="C88" t="s">
+        <v>55</v>
+      </c>
+      <c r="D88" t="s">
+        <v>140</v>
+      </c>
+      <c r="E88" t="s">
+        <v>128</v>
+      </c>
+      <c r="F88">
+        <v>3</v>
+      </c>
+      <c r="G88" s="1">
+        <v>-0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>6</v>
+      </c>
+      <c r="B89">
+        <v>13</v>
+      </c>
+      <c r="C89" t="s">
+        <v>272</v>
+      </c>
+      <c r="D89" t="s">
+        <v>156</v>
+      </c>
+      <c r="E89" t="s">
+        <v>47</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>6</v>
+      </c>
+      <c r="B90">
+        <v>14</v>
+      </c>
+      <c r="C90" t="s">
+        <v>106</v>
+      </c>
+      <c r="D90" t="s">
+        <v>131</v>
+      </c>
+      <c r="E90" t="s">
+        <v>47</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>6</v>
+      </c>
+      <c r="B91">
+        <v>15</v>
+      </c>
+      <c r="C91" t="s">
+        <v>109</v>
+      </c>
+      <c r="D91" t="s">
+        <v>144</v>
+      </c>
+      <c r="E91" t="s">
+        <v>128</v>
+      </c>
+      <c r="F91">
+        <v>2</v>
+      </c>
+      <c r="G91" s="1">
         <v>0</v>
       </c>
     </row>
